--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -15,9 +15,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'item_taxonomia'!$A$1:$C$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'template'!$A$1:$D$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'item_template'!$A$1:$G$133</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'schema'!$A$1:$D$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'item_schema'!$A$1:$F$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'item_template'!$A$1:$G$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'schema'!$A$1:$D$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'item_schema'!$A$1:$F$99</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4963,8 +4963,107 @@
         </is>
       </c>
     </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>section_start</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Embalagens\s+e\s+Preservantes</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>descricao=Identifica o inicio da secao de Embalagens e Preservantes.</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Nao se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>table_header</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>\bEmbalagem\b\s+\bVolume\b\s+Preserva..o\s+M.todos</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>descricao=Identifica o cabecalho da tabela de embalagens e preservantes.</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Nao se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>sample_identification</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>^\s*\d+\s*-\s*.+$</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>descricao=Identifica a linha da amostra associada ao quadro.</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Nao se aplica</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G133"/>
+  <autoFilter ref="A1:G137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4975,7 +5074,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="13.54296875" customWidth="1" min="1" max="1"/>
@@ -5132,8 +5231,26 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Verdadeiro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D8"/>
+  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5144,7 +5261,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9.7265625" customWidth="1" min="1" max="1"/>
@@ -7679,8 +7796,260 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="n">
+        <v>8</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="n">
+        <v>8</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="n">
+        <v>8</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="n">
+        <v>8</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>id_sample</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="n">
+        <v>8</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>identificacao_amostra</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" t="n">
+        <v>8</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>embalagem</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="n">
+        <v>8</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>volume</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="n">
+        <v>8</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>preservacao</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="n">
+        <v>8</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>metodos</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F89"/>
+  <autoFilter ref="A1:F99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -5570,7 +5570,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>resultado_tratado</t>
+          <t>acm_resultado_tratado</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>qualificador</t>
+          <t>acm_qualificador</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>unidade</t>
+          <t>acm_unidade</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5738,7 +5738,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>conama_operador</t>
+          <t>acm_conama_operador</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>conama_minimo</t>
+          <t>acm_conama_minimo</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>conama_maximo</t>
+          <t>acm_conama_maximo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5822,7 +5822,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>conama_unidade</t>
+          <t>acm_conama_unidade</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -5878,7 +5878,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>copam_cerh_operador</t>
+          <t>acm_copam_cerh_operador</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -5906,7 +5906,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>copam_cerh_minimo</t>
+          <t>acm_copam_cerh_minimo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -5934,7 +5934,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>copam_cerh_maximo</t>
+          <t>acm_copam_cerh_maximo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -5962,7 +5962,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>copam_cerh_unidade</t>
+          <t>acm_copam_cerh_unidade</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ld_minimo</t>
+          <t>acm_ld_minimo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -6046,7 +6046,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>ld_maximo</t>
+          <t>acm_ld_maximo</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ld_unidade</t>
+          <t>acm_ld_unidade</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>lq_minimo</t>
+          <t>acm_lq_minimo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>lq_maximo</t>
+          <t>acm_lq_maximo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>lq_unidade</t>
+          <t>acm_lq_unidade</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -6270,7 +6270,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>incerteza_valor</t>
+          <t>acm_incerteza_valor</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6298,7 +6298,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>incerteza_unidade</t>
+          <t>acm_incerteza_unidade</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>faixa_aceitacao_operador</t>
+          <t>acm_faixa_aceitacao_operador</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>faixa_aceitacao_minimo</t>
+          <t>acm_faixa_aceitacao_minimo</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>faixa_aceitacao_maximo</t>
+          <t>acm_faixa_aceitacao_maximo</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6494,7 +6494,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>faixa_aceitacao_unidade</t>
+          <t>acm_faixa_aceitacao_unidade</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -5402,7 +5402,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>id_sample</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -7894,7 +7894,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>id_sample</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G137"/>
+  <dimension ref="A1:G141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5062,6 +5062,138 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>(?:^|\n)\s*Notas?\s*:?\s*(.*?)(?=\n\s*(?:Considera..es\s+Gerais|Declara..o\s+de\s+Conformidade|Chave\s+de\s+Valida..o|$))</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>descricao=Extrai o bloco textual de Notas.</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>N?o se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>(?:^|\n)\s*Considera..es\s+Gerais\s*:?\s*(.*?)(?=\n\s*(?:Declara..o\s+de\s+Conformidade|Chave\s+de\s+Valida..o|Notas?|$))</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>descricao=Extrai o bloco textual de Consideracoes Gerais.</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>N?o se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>(?:^|\n)\s*Declara..o\s+de\s+Conformidade\s*:?\s*(.*?)(?=\n\s*(?:Chave\s+de\s+Valida..o|Considera..es\s+Gerais|Notas?|$))</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>descricao=Extrai o bloco textual de Declaracao de Conformidade.</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>N?o se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>chave_validacao</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>(?:^|\n)\s*Chave\s+de\s+Valida..o\s*:?\s*([A-Za-z0-9][A-Za-z0-9\-_.]+)</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>descricao=Extrai a chave de validacao do laudo.</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>N?o se aplica</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5074,7 +5206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="13.54296875" customWidth="1" min="1" max="1"/>
@@ -5244,6 +5376,78 @@
         </is>
       </c>
       <c r="D9" t="inlineStr">
+        <is>
+          <t>Verdadeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Verdadeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Verdadeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Verdadeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Verdadeiro</t>
         </is>
@@ -5261,7 +5465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9.7265625" customWidth="1" min="1" max="1"/>
@@ -8048,6 +8252,678 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="n">
+        <v>9</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="n">
+        <v>9</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="n">
+        <v>9</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="n">
+        <v>9</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>id_amostra</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="n">
+        <v>9</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>pagina</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="n">
+        <v>9</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="n">
+        <v>10</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="n">
+        <v>10</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="n">
+        <v>10</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="n">
+        <v>10</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>id_amostra</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="n">
+        <v>10</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>pagina</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="n">
+        <v>10</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="n">
+        <v>11</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="n">
+        <v>11</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="n">
+        <v>11</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="n">
+        <v>11</v>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>id_amostra</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="n">
+        <v>11</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>pagina</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="n">
+        <v>11</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="n">
+        <v>12</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="n">
+        <v>12</v>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="n">
+        <v>12</v>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="n">
+        <v>12</v>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>id_amostra</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>121</v>
+      </c>
+      <c r="B122" t="n">
+        <v>12</v>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>pagina</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>122</v>
+      </c>
+      <c r="B123" t="n">
+        <v>12</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>chave_validacao</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="item_taxonomia" sheetId="1" state="visible" r:id="rId1"/>
@@ -60,7 +60,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -83,16 +83,30 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9EADCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9EADCC"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -511,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12.54296875" customWidth="1" min="1" max="1"/>
@@ -531,7 +545,7 @@
           <t>id_item_taxonomia</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>regex</t>
         </is>
@@ -539,6 +553,11 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>ativo</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>versao</t>
         </is>
       </c>
     </row>
@@ -558,6 +577,9 @@
         <is>
           <t>Verdadeiro</t>
         </is>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1860,7 +1882,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1891,7 +1913,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1922,7 +1944,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1953,7 +1975,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -1984,7 +2006,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -2015,7 +2037,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -2046,7 +2068,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -2077,7 +2099,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -2108,7 +2130,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -2139,7 +2161,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -2170,7 +2192,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -2201,7 +2223,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -2232,7 +2254,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -2263,7 +2285,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -2294,7 +2316,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -2325,7 +2347,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -2356,7 +2378,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -2387,7 +2409,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -2418,7 +2440,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -2449,7 +2471,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -2480,7 +2502,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -2511,7 +2533,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -2542,7 +2564,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>NÃO SE APLICA</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -5465,7 +5487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F123"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9.7265625" customWidth="1" min="1" max="1"/>
@@ -5606,12 +5628,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>versao</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5634,12 +5656,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>tipo</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro_ou_texto</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5662,7 +5684,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>categoria</t>
+          <t>tipo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5690,7 +5712,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>subcategoria</t>
+          <t>categoria</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5718,7 +5740,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>subcategoria</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5746,7 +5768,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5774,12 +5796,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>acm_resultado_tratado</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -5802,12 +5824,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>acm_qualificador</t>
+          <t>acm_resultado_tratado</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -5830,7 +5852,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>acm_unidade</t>
+          <t>acm_qualificador</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5858,7 +5880,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>acm_unidade</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5886,12 +5908,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>data_inicio</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -5914,12 +5936,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>conama</t>
+          <t>data_inicio</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -5942,7 +5964,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>acm_conama_operador</t>
+          <t>conama</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -5970,12 +5992,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>acm_conama_minimo</t>
+          <t>acm_conama_operador</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -5998,7 +6020,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>acm_conama_maximo</t>
+          <t>acm_conama_minimo</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6026,12 +6048,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>acm_conama_unidade</t>
+          <t>acm_conama_maximo</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -6054,7 +6076,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>copam_cerh</t>
+          <t>acm_conama_unidade</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -6082,7 +6104,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_operador</t>
+          <t>copam_cerh</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -6110,12 +6132,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_minimo</t>
+          <t>acm_copam_cerh_operador</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -6138,7 +6160,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_maximo</t>
+          <t>acm_copam_cerh_minimo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -6166,12 +6188,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_unidade</t>
+          <t>acm_copam_cerh_maximo</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -6194,7 +6216,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>ld</t>
+          <t>acm_copam_cerh_unidade</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -6222,12 +6244,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>acm_ld_minimo</t>
+          <t>ld</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6250,7 +6272,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>acm_ld_maximo</t>
+          <t>acm_ld_minimo</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6278,12 +6300,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>acm_ld_unidade</t>
+          <t>acm_ld_maximo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -6306,7 +6328,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>lq</t>
+          <t>acm_ld_unidade</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6334,12 +6356,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>acm_lq_minimo</t>
+          <t>lq</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6362,7 +6384,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>acm_lq_maximo</t>
+          <t>acm_lq_minimo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -6390,12 +6412,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>acm_lq_unidade</t>
+          <t>acm_lq_maximo</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6418,7 +6440,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>referencia</t>
+          <t>acm_lq_unidade</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -6446,7 +6468,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>incerteza</t>
+          <t>referencia</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6474,12 +6496,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>acm_incerteza_valor</t>
+          <t>incerteza</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6502,12 +6524,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>acm_incerteza_unidade</t>
+          <t>acm_incerteza_valor</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -6530,7 +6552,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>numero_cq</t>
+          <t>acm_incerteza_unidade</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -6558,12 +6580,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>duplicata</t>
+          <t>numero_cq</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>texto_numerico</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -6586,12 +6608,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>faixa_aceitacao</t>
+          <t>duplicata</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>texto_numerico</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -6614,7 +6636,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_operador</t>
+          <t>faixa_aceitacao</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6642,12 +6664,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_minimo</t>
+          <t>acm_faixa_aceitacao_operador</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -6670,7 +6692,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_maximo</t>
+          <t>acm_faixa_aceitacao_minimo</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6698,12 +6720,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_unidade</t>
+          <t>acm_faixa_aceitacao_maximo</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -6726,12 +6748,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>variacao_percentual</t>
+          <t>acm_faixa_aceitacao_unidade</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -6754,7 +6776,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>quantidade_adicionada</t>
+          <t>variacao_percentual</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6782,7 +6804,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>recuperacao_percentual</t>
+          <t>quantidade_adicionada</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -6801,21 +6823,21 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>results_extract</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>recuperacao_percentual</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6838,12 +6860,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -6866,12 +6888,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro_ou_texto</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -6894,12 +6916,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -6922,7 +6944,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>versao</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -6950,12 +6972,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>tipo_amostra</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro_ou_texto</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -6978,7 +7000,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>criterio_conformidade</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -7006,12 +7028,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>tipo_amostra</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7034,12 +7056,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>dh_coleta</t>
+          <t>criterio_conformidade</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7062,7 +7084,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>data_publicacao</t>
+          <t>data_coleta</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -7090,7 +7112,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>dh_publicacao</t>
+          <t>dh_coleta</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -7118,7 +7140,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>data_recebimento</t>
+          <t>data_publicacao</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7146,7 +7168,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>dh_recebimento</t>
+          <t>dh_publicacao</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7174,12 +7196,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>observacoes</t>
+          <t>data_recebimento</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7202,12 +7224,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>dh_inicio_atividade</t>
+          <t>dh_recebimento</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>data_ou_data_hora</t>
+          <t>hora</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7230,7 +7252,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>localizacao</t>
+          <t>observacoes</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -7258,12 +7280,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>dh_inicio_atividade</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>data_ou_data_hora</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7286,12 +7308,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>localizacao</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7314,12 +7336,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>coordenadas</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7342,12 +7364,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>clima_ultimas_24h</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7370,7 +7392,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>coordenadas</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7398,7 +7420,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>tipo_coleta</t>
+          <t>clima_ultimas_24h</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7426,7 +7448,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>responsavel_amostra</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7454,7 +7476,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>planejamento_amostragem</t>
+          <t>tipo_coleta</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7482,7 +7504,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>descricao_nao_conformidade</t>
+          <t>responsavel_amostra</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7501,16 +7523,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>planejamento_amostragem</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7529,21 +7551,21 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>descricao_nao_conformidade</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7566,7 +7588,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7594,7 +7616,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7622,7 +7644,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>proposta_comercial</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7650,7 +7672,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>cliente</t>
+          <t>versao</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7678,12 +7700,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>cnpj_cpf</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro_ou_texto</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7706,7 +7728,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>contato</t>
+          <t>proposta_comercial</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7734,7 +7756,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>telefone</t>
+          <t>cliente</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7762,7 +7784,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>endereco</t>
+          <t>cnpj_cpf</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7781,21 +7803,21 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>table_extraction_audit_estrutura</t>
+          <t>contato</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>estrutura_auditoria</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7809,21 +7831,21 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>classification_audit_estrutura</t>
+          <t>telefone</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>estrutura_auditoria</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7837,21 +7859,21 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>validation_errors_estrutura</t>
+          <t>endereco</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>estrutura_auditoria</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -7865,21 +7887,21 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7893,21 +7915,21 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>inteiro_ou_texto</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -7921,21 +7943,21 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7949,21 +7971,21 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>versao</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7977,21 +7999,21 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>subtipo_amostra</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -8005,21 +8027,21 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>tabela_indice</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -8033,21 +8055,21 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>categoria</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -8061,16 +8083,16 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>subcategoria</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8089,21 +8111,21 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>tipo_registro</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -8117,16 +8139,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>modo_auditoria</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8145,16 +8167,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>embalagem</t>
+          <t>cabecalho_detectado</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8173,16 +8195,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>colunas_detectadas</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8201,16 +8223,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>preservacao</t>
+          <t>colunas_mapeadas</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8229,16 +8251,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>colunas_sem_mapeamento</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8257,16 +8279,16 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>campos_esperados</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -8285,21 +8307,21 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>campos_obrigatorios_ausentes</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8313,16 +8335,16 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>campos_opcionais_ausentes</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -8341,21 +8363,21 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>usou_fallback</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8369,21 +8391,21 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8397,16 +8419,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>observacao</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8425,21 +8447,21 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>classification_audit_estrutura</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>estrutura_auditoria</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -8453,21 +8475,21 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>validation_errors_estrutura</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>estrutura_auditoria</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8481,21 +8503,21 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro_ou_texto</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8509,21 +8531,21 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8537,21 +8559,21 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8565,21 +8587,21 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_coleta</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8593,16 +8615,16 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>subtipo_amostra</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8621,21 +8643,21 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -8649,21 +8671,21 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro_ou_texto</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -8677,21 +8699,21 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -8705,21 +8727,21 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>versao</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -8733,21 +8755,21 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro_ou_texto</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -8761,16 +8783,16 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -8789,21 +8811,21 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>embalagem</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -8817,16 +8839,16 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -8845,21 +8867,21 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>preservacao</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -8873,21 +8895,21 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -8901,24 +8923,780 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
+        <v>9</v>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>123</v>
+      </c>
+      <c r="B124" t="n">
+        <v>9</v>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>124</v>
+      </c>
+      <c r="B125" t="n">
+        <v>9</v>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>125</v>
+      </c>
+      <c r="B126" t="n">
+        <v>9</v>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>versao</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="n">
+        <v>9</v>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>id_amostra</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="n">
+        <v>127</v>
+      </c>
+      <c r="B128" t="n">
+        <v>9</v>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>pagina</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" t="n">
+        <v>9</v>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" t="n">
+        <v>10</v>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="n">
+        <v>130</v>
+      </c>
+      <c r="B131" t="n">
+        <v>10</v>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="n">
+        <v>131</v>
+      </c>
+      <c r="B132" t="n">
+        <v>10</v>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="n">
+        <v>132</v>
+      </c>
+      <c r="B133" t="n">
+        <v>10</v>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>versao</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>133</v>
+      </c>
+      <c r="B134" t="n">
+        <v>10</v>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>id_amostra</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>134</v>
+      </c>
+      <c r="B135" t="n">
+        <v>10</v>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>pagina</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>135</v>
+      </c>
+      <c r="B136" t="n">
+        <v>10</v>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>136</v>
+      </c>
+      <c r="B137" t="n">
+        <v>11</v>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="n">
+        <v>11</v>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>138</v>
+      </c>
+      <c r="B139" t="n">
+        <v>11</v>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="n">
+        <v>11</v>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>versao</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>140</v>
+      </c>
+      <c r="B141" t="n">
+        <v>11</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>id_amostra</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>11</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>pagina</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>11</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>143</v>
+      </c>
+      <c r="B144" t="n">
         <v>12</v>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C144" t="inlineStr">
         <is>
           <t>validation_key</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" t="n">
+        <v>12</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" t="n">
+        <v>12</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" t="n">
+        <v>12</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>versao</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="n">
+        <v>12</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>id_amostra</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>inteiro_ou_texto</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="n">
+        <v>12</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>pagina</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" t="n">
+        <v>12</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
         <is>
           <t>chave_validacao</t>
         </is>
       </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
         <is>
           <t>sim</t>
         </is>

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -651,7 +651,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>template_required</t>
+          <t>template_detection</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -666,7 +666,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>peso=0</t>
+          <t>rule_type=required; peso=0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>template_required</t>
+          <t>template_detection</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>peso=0</t>
+          <t>rule_type=required; peso=0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>template_required</t>
+          <t>template_detection</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>peso=0</t>
+          <t>rule_type=required; peso=0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>template_required</t>
+          <t>template_detection</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>peso=0</t>
+          <t>rule_type=required; peso=0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -783,7 +783,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>template_positive</t>
+          <t>template_detection</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>peso=40</t>
+          <t>rule_type=positive; peso=40</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>template_positive</t>
+          <t>template_detection</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -831,7 +831,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>peso=40</t>
+          <t>rule_type=positive; peso=40</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>template_positive</t>
+          <t>template_detection</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>peso=20</t>
+          <t>rule_type=positive; peso=20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>template_negative</t>
+          <t>template_detection</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>peso=0</t>
+          <t>rule_type=negative; peso=0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>template_negative</t>
+          <t>template_detection</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>peso=0</t>
+          <t>rule_type=negative; peso=0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -5228,7 +5228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="13.54296875" customWidth="1" min="1" max="1"/>
@@ -5472,6 +5472,132 @@
       <c r="D13" t="inlineStr">
         <is>
           <t>Verdadeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>template_detection</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Falso</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>category_alias</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Falso</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>category_type</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Falso</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>continuation</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Falso</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>header_alias</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Falso</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>layout</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Falso</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>subcategory_alias</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Falso</t>
         </is>
       </c>
     </row>

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -5228,7 +5228,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="13.54296875" customWidth="1" min="1" max="1"/>
@@ -5598,6 +5598,24 @@
       <c r="D20" t="inlineStr">
         <is>
           <t>Falso</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Verdadeiro</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F150"/>
+  <dimension ref="A1:F166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9.7265625" customWidth="1" min="1" max="1"/>
@@ -9828,6 +9846,454 @@
         </is>
       </c>
     </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>150</v>
+      </c>
+      <c r="B151" t="n">
+        <v>20</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>151</v>
+      </c>
+      <c r="B152" t="n">
+        <v>20</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>caminho_arquivo</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="n">
+        <v>20</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>153</v>
+      </c>
+      <c r="B154" t="n">
+        <v>20</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>154</v>
+      </c>
+      <c r="B155" t="n">
+        <v>20</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>versao</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>155</v>
+      </c>
+      <c r="B156" t="n">
+        <v>20</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>id_amostra</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>156</v>
+      </c>
+      <c r="B157" t="n">
+        <v>20</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>identificacao_amostra</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>157</v>
+      </c>
+      <c r="B158" t="n">
+        <v>20</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>data_publicacao</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="n">
+        <v>158</v>
+      </c>
+      <c r="B159" t="n">
+        <v>20</v>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>data_coleta</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="n">
+        <v>159</v>
+      </c>
+      <c r="B160" t="n">
+        <v>20</v>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>hash_arquivo</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="n">
+        <v>160</v>
+      </c>
+      <c r="B161" t="n">
+        <v>20</v>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>hash_texto</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="n">
+        <v>161</v>
+      </c>
+      <c r="B162" t="n">
+        <v>20</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>grupo_duplicidade</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="n">
+        <v>162</v>
+      </c>
+      <c r="B163" t="n">
+        <v>20</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>tipo_duplicidade</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="n">
+        <v>163</v>
+      </c>
+      <c r="B164" t="n">
+        <v>20</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>arquivo_referencia</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="n">
+        <v>164</v>
+      </c>
+      <c r="B165" t="n">
+        <v>20</v>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>motivo</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="n">
+        <v>20</v>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G141"/>
+  <dimension ref="A1:G143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Planejamento de Amostragem:\s*(.*?)(?:\s+conformidade|\n)</t>
+          <t>Planejamento de Amostragem:\s*(CA\d+/\d{4})</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>(?:^|\n)\s*Chave\s+de\s+Valida..o\s*:?\s*([A-Za-z0-9][A-Za-z0-9\-_.]+)</t>
+          <t>(?:^|\n)\s*Chave\s+de\s+Valida..o\s*:?\s*((?!FO-ANL-\d+\b)[A-Za-z0-9][A-Za-z0-9\-_.]{7,})</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5211,6 +5211,72 @@
         </is>
       </c>
       <c r="G141" t="inlineStr">
+        <is>
+          <t>N?o se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>141</v>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>metadata</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>codigo_laudo</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>(Relat.rio Anal.tico\s*\d+/\d+\.\d+(?:\.[A-Z]{1,2})?)</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>N?o se aplica</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>N?o se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>142</v>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>codigo_laudo_substituido</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>(Este\s+relat.rio\s+anal.tico\s+cancela\s+e\s+substitui\s+o\s+relat.rio\s+\d+/\d+\.\d+)</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>N?o se aplica</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
         <is>
           <t>N?o se aplica</t>
         </is>
@@ -5631,7 +5697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:F169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9.7265625" customWidth="1" min="1" max="1"/>
@@ -5721,7 +5787,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5777,7 +5843,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5805,7 +5871,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5912,7 +5978,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>codigo_laudo</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5940,7 +6006,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>codigo_laudo_substituido</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5968,12 +6034,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>acm_resultado_tratado</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -5996,7 +6062,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>acm_qualificador</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6024,12 +6090,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>acm_unidade</t>
+          <t>acm_resultado_tratado</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -6052,7 +6118,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>acm_qualificador</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6080,12 +6146,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>data_inicio</t>
+          <t>acm_unidade</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -6108,7 +6174,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>conama</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6136,12 +6202,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>acm_conama_operador</t>
+          <t>data_inicio</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -6164,12 +6230,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>acm_conama_minimo</t>
+          <t>conama</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -6192,12 +6258,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>acm_conama_maximo</t>
+          <t>acm_conama_operador</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -6220,12 +6286,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>acm_conama_unidade</t>
+          <t>acm_conama_minimo</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -6248,12 +6314,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>copam_cerh</t>
+          <t>acm_conama_maximo</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6276,7 +6342,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_operador</t>
+          <t>acm_conama_unidade</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -6304,12 +6370,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_minimo</t>
+          <t>copam_cerh</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -6332,12 +6398,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_maximo</t>
+          <t>acm_copam_cerh_operador</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -6360,12 +6426,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_unidade</t>
+          <t>acm_copam_cerh_minimo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -6388,12 +6454,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ld</t>
+          <t>acm_copam_cerh_maximo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6416,12 +6482,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>acm_ld_minimo</t>
+          <t>acm_copam_cerh_unidade</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -6444,12 +6510,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>acm_ld_maximo</t>
+          <t>ld</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -6472,12 +6538,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>acm_ld_unidade</t>
+          <t>acm_ld_minimo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6500,12 +6566,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>lq</t>
+          <t>acm_ld_maximo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6528,12 +6594,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>acm_lq_minimo</t>
+          <t>acm_ld_unidade</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6556,12 +6622,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>acm_lq_maximo</t>
+          <t>lq</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6584,12 +6650,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>acm_lq_unidade</t>
+          <t>acm_lq_minimo</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6612,12 +6678,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>referencia</t>
+          <t>acm_lq_maximo</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6640,7 +6706,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>incerteza</t>
+          <t>acm_lq_unidade</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -6668,12 +6734,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>acm_incerteza_valor</t>
+          <t>referencia</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -6696,7 +6762,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>acm_incerteza_unidade</t>
+          <t>incerteza</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -6724,12 +6790,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>numero_cq</t>
+          <t>acm_incerteza_valor</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -6752,12 +6818,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>duplicata</t>
+          <t>acm_incerteza_unidade</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>texto_numerico</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -6780,7 +6846,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>faixa_aceitacao</t>
+          <t>numero_cq</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6808,12 +6874,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_operador</t>
+          <t>duplicata</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>texto_numerico</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -6836,12 +6902,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_minimo</t>
+          <t>faixa_aceitacao</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -6864,12 +6930,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_maximo</t>
+          <t>acm_faixa_aceitacao_operador</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -6892,12 +6958,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_unidade</t>
+          <t>acm_faixa_aceitacao_minimo</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -6920,7 +6986,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>variacao_percentual</t>
+          <t>acm_faixa_aceitacao_maximo</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6948,12 +7014,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>quantidade_adicionada</t>
+          <t>acm_faixa_aceitacao_unidade</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6976,7 +7042,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>recuperacao_percentual</t>
+          <t>variacao_percentual</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -6995,21 +7061,21 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>results_extract</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>quantidade_adicionada</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -7023,21 +7089,21 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>results_extract</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>recuperacao_percentual</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -7051,16 +7117,16 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -7079,21 +7145,21 @@
         <v>51</v>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -7107,21 +7173,21 @@
         <v>52</v>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -7135,21 +7201,21 @@
         <v>53</v>
       </c>
       <c r="B54" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>versao</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -7163,21 +7229,21 @@
         <v>54</v>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>tipo_amostra</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7191,16 +7257,16 @@
         <v>55</v>
       </c>
       <c r="B56" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>criterio_conformidade</t>
+          <t>proposta_comercial</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -7219,21 +7285,21 @@
         <v>56</v>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>cliente</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7247,21 +7313,21 @@
         <v>57</v>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>dh_coleta</t>
+          <t>cnpj_cpf</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -7275,21 +7341,21 @@
         <v>58</v>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>data_publicacao</t>
+          <t>contato</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -7303,21 +7369,21 @@
         <v>59</v>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>dh_publicacao</t>
+          <t>telefone</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -7331,21 +7397,21 @@
         <v>60</v>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>data_recebimento</t>
+          <t>endereco</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7359,21 +7425,21 @@
         <v>61</v>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>dh_recebimento</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7387,21 +7453,21 @@
         <v>62</v>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>observacoes</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7415,21 +7481,21 @@
         <v>63</v>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>dh_inicio_atividade</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>data_ou_data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7443,21 +7509,21 @@
         <v>64</v>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>localizacao</t>
+          <t>versao</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7471,21 +7537,21 @@
         <v>65</v>
       </c>
       <c r="B66" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7499,21 +7565,21 @@
         <v>66</v>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>tabela_indice</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7527,16 +7593,16 @@
         <v>67</v>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>coordenadas</t>
+          <t>categoria</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7555,16 +7621,16 @@
         <v>68</v>
       </c>
       <c r="B69" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>clima_ultimas_24h</t>
+          <t>subcategoria</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7583,16 +7649,16 @@
         <v>69</v>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>tipo_registro</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7611,16 +7677,16 @@
         <v>70</v>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>tipo_coleta</t>
+          <t>modo_auditoria</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7639,16 +7705,16 @@
         <v>71</v>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>responsavel_amostra</t>
+          <t>cabecalho_detectado</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7667,16 +7733,16 @@
         <v>72</v>
       </c>
       <c r="B73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>planejamento_amostragem</t>
+          <t>colunas_detectadas</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -7695,16 +7761,16 @@
         <v>73</v>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>descricao_nao_conformidade</t>
+          <t>colunas_mapeadas</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7723,16 +7789,16 @@
         <v>74</v>
       </c>
       <c r="B75" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>colunas_sem_mapeamento</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7751,21 +7817,21 @@
         <v>75</v>
       </c>
       <c r="B76" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>campos_esperados</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7779,16 +7845,16 @@
         <v>76</v>
       </c>
       <c r="B77" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>campos_obrigatorios_ausentes</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7807,16 +7873,16 @@
         <v>77</v>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>campos_opcionais_ausentes</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7835,21 +7901,21 @@
         <v>78</v>
       </c>
       <c r="B79" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>usou_fallback</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -7863,16 +7929,16 @@
         <v>79</v>
       </c>
       <c r="B80" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>proposta_comercial</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7891,16 +7957,16 @@
         <v>80</v>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>cliente</t>
+          <t>observacao</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7919,21 +7985,21 @@
         <v>81</v>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>cnpj_cpf</t>
+          <t>classification_audit_estrutura</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>estrutura_auditoria</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7947,21 +8013,21 @@
         <v>82</v>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>contato</t>
+          <t>validation_errors_estrutura</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>estrutura_auditoria</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7975,21 +8041,21 @@
         <v>83</v>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>telefone</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8003,21 +8069,21 @@
         <v>84</v>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>endereco</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8031,21 +8097,21 @@
         <v>85</v>
       </c>
       <c r="B86" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -8059,21 +8125,21 @@
         <v>86</v>
       </c>
       <c r="B87" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>data_coleta</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>data</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -8087,16 +8153,16 @@
         <v>87</v>
       </c>
       <c r="B88" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>subtipo_amostra</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8115,16 +8181,16 @@
         <v>88</v>
       </c>
       <c r="B89" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8143,16 +8209,16 @@
         <v>89</v>
       </c>
       <c r="B90" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8171,21 +8237,21 @@
         <v>90</v>
       </c>
       <c r="B91" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>tabela_indice</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -8199,21 +8265,21 @@
         <v>91</v>
       </c>
       <c r="B92" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>categoria</t>
+          <t>versao</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -8227,21 +8293,21 @@
         <v>92</v>
       </c>
       <c r="B93" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>subcategoria</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -8255,16 +8321,16 @@
         <v>93</v>
       </c>
       <c r="B94" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>tipo_registro</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8283,16 +8349,16 @@
         <v>94</v>
       </c>
       <c r="B95" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>modo_auditoria</t>
+          <t>embalagem</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8311,16 +8377,16 @@
         <v>95</v>
       </c>
       <c r="B96" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>cabecalho_detectado</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8339,16 +8405,16 @@
         <v>96</v>
       </c>
       <c r="B97" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>colunas_detectadas</t>
+          <t>preservacao</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -8367,16 +8433,16 @@
         <v>97</v>
       </c>
       <c r="B98" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>colunas_mapeadas</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8395,16 +8461,16 @@
         <v>98</v>
       </c>
       <c r="B99" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>colunas_sem_mapeamento</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -8423,21 +8489,21 @@
         <v>99</v>
       </c>
       <c r="B100" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>campos_esperados</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8451,16 +8517,16 @@
         <v>100</v>
       </c>
       <c r="B101" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>campos_obrigatorios_ausentes</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8479,21 +8545,21 @@
         <v>101</v>
       </c>
       <c r="B102" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>campos_opcionais_ausentes</t>
+          <t>versao</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8507,21 +8573,21 @@
         <v>102</v>
       </c>
       <c r="B103" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>usou_fallback</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8535,21 +8601,21 @@
         <v>103</v>
       </c>
       <c r="B104" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8563,16 +8629,16 @@
         <v>104</v>
       </c>
       <c r="B105" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>observacao</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8591,21 +8657,21 @@
         <v>105</v>
       </c>
       <c r="B106" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>classification_audit_estrutura</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>estrutura_auditoria</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -8619,21 +8685,21 @@
         <v>106</v>
       </c>
       <c r="B107" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>validation_errors_estrutura</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>estrutura_auditoria</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8647,21 +8713,21 @@
         <v>107</v>
       </c>
       <c r="B108" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8675,21 +8741,21 @@
         <v>108</v>
       </c>
       <c r="B109" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>versao</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8703,21 +8769,21 @@
         <v>109</v>
       </c>
       <c r="B110" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8731,21 +8797,21 @@
         <v>110</v>
       </c>
       <c r="B111" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8759,16 +8825,16 @@
         <v>111</v>
       </c>
       <c r="B112" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>subtipo_amostra</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8787,11 +8853,11 @@
         <v>112</v>
       </c>
       <c r="B113" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -8815,11 +8881,11 @@
         <v>113</v>
       </c>
       <c r="B114" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -8829,7 +8895,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -8843,11 +8909,11 @@
         <v>114</v>
       </c>
       <c r="B115" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -8871,11 +8937,11 @@
         <v>115</v>
       </c>
       <c r="B116" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -8885,7 +8951,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -8899,11 +8965,11 @@
         <v>116</v>
       </c>
       <c r="B117" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -8913,7 +8979,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -8927,21 +8993,21 @@
         <v>117</v>
       </c>
       <c r="B118" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -8955,16 +9021,16 @@
         <v>118</v>
       </c>
       <c r="B119" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>embalagem</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -8983,16 +9049,16 @@
         <v>119</v>
       </c>
       <c r="B120" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -9011,21 +9077,21 @@
         <v>120</v>
       </c>
       <c r="B121" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>preservacao</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -9039,16 +9105,16 @@
         <v>121</v>
       </c>
       <c r="B122" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -9067,21 +9133,21 @@
         <v>122</v>
       </c>
       <c r="B123" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>versao</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -9095,21 +9161,21 @@
         <v>123</v>
       </c>
       <c r="B124" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -9123,21 +9189,21 @@
         <v>124</v>
       </c>
       <c r="B125" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -9151,16 +9217,16 @@
         <v>125</v>
       </c>
       <c r="B126" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>chave_validacao</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -9179,21 +9245,21 @@
         <v>126</v>
       </c>
       <c r="B127" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -9207,21 +9273,21 @@
         <v>127</v>
       </c>
       <c r="B128" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>caminho_arquivo</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -9235,21 +9301,21 @@
         <v>128</v>
       </c>
       <c r="B129" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -9263,16 +9329,16 @@
         <v>129</v>
       </c>
       <c r="B130" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -9291,21 +9357,21 @@
         <v>130</v>
       </c>
       <c r="B131" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>versao</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -9319,21 +9385,21 @@
         <v>131</v>
       </c>
       <c r="B132" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -9347,16 +9413,16 @@
         <v>132</v>
       </c>
       <c r="B133" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -9375,21 +9441,21 @@
         <v>133</v>
       </c>
       <c r="B134" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>data_publicacao</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -9403,21 +9469,21 @@
         <v>134</v>
       </c>
       <c r="B135" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>data_coleta</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -9431,16 +9497,16 @@
         <v>135</v>
       </c>
       <c r="B136" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>hash_arquivo</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9459,16 +9525,16 @@
         <v>136</v>
       </c>
       <c r="B137" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>hash_texto</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9487,21 +9553,21 @@
         <v>137</v>
       </c>
       <c r="B138" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>grupo_duplicidade</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -9515,16 +9581,16 @@
         <v>138</v>
       </c>
       <c r="B139" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>tipo_duplicidade</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9543,16 +9609,16 @@
         <v>139</v>
       </c>
       <c r="B140" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>arquivo_referencia</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9571,21 +9637,21 @@
         <v>140</v>
       </c>
       <c r="B141" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>motivo</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -9599,21 +9665,21 @@
         <v>141</v>
       </c>
       <c r="B142" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -9627,16 +9693,16 @@
         <v>142</v>
       </c>
       <c r="B143" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9655,21 +9721,21 @@
         <v>143</v>
       </c>
       <c r="B144" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -9683,21 +9749,21 @@
         <v>144</v>
       </c>
       <c r="B145" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -9711,21 +9777,21 @@
         <v>145</v>
       </c>
       <c r="B146" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>versao</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -9739,21 +9805,21 @@
         <v>146</v>
       </c>
       <c r="B147" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -9767,21 +9833,21 @@
         <v>147</v>
       </c>
       <c r="B148" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>inteiro_ou_texto</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9795,21 +9861,21 @@
         <v>148</v>
       </c>
       <c r="B149" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>tipo_amostra</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9823,16 +9889,16 @@
         <v>149</v>
       </c>
       <c r="B150" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>chave_validacao</t>
+          <t>criterio_conformidade</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9851,21 +9917,21 @@
         <v>150</v>
       </c>
       <c r="B151" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>data_coleta</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9879,21 +9945,21 @@
         <v>151</v>
       </c>
       <c r="B152" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>caminho_arquivo</t>
+          <t>dh_coleta</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>hora</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -9907,21 +9973,21 @@
         <v>152</v>
       </c>
       <c r="B153" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>data_publicacao</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -9935,21 +10001,21 @@
         <v>153</v>
       </c>
       <c r="B154" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>dh_publicacao</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>hora</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -9963,21 +10029,21 @@
         <v>154</v>
       </c>
       <c r="B155" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>data_recebimento</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -9991,21 +10057,21 @@
         <v>155</v>
       </c>
       <c r="B156" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>dh_recebimento</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>hora</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -10019,16 +10085,16 @@
         <v>156</v>
       </c>
       <c r="B157" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>observacoes</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -10047,21 +10113,21 @@
         <v>157</v>
       </c>
       <c r="B158" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>data_publicacao</t>
+          <t>dh_inicio_atividade</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_ou_data_hora</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -10075,16 +10141,16 @@
         <v>158</v>
       </c>
       <c r="B159" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>localizacao</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -10103,21 +10169,21 @@
         <v>159</v>
       </c>
       <c r="B160" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>hash_arquivo</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -10131,21 +10197,21 @@
         <v>160</v>
       </c>
       <c r="B161" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>hash_texto</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -10159,16 +10225,16 @@
         <v>161</v>
       </c>
       <c r="B162" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>grupo_duplicidade</t>
+          <t>coordenadas</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10187,16 +10253,16 @@
         <v>162</v>
       </c>
       <c r="B163" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>tipo_duplicidade</t>
+          <t>clima_ultimas_24h</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10215,16 +10281,16 @@
         <v>163</v>
       </c>
       <c r="B164" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>arquivo_referencia</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10243,16 +10309,16 @@
         <v>164</v>
       </c>
       <c r="B165" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>motivo</t>
+          <t>tipo_coleta</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10271,16 +10337,16 @@
         <v>165</v>
       </c>
       <c r="B166" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>responsavel_amostra</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10289,6 +10355,90 @@
         </is>
       </c>
       <c r="F166" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>166</v>
+      </c>
+      <c r="B167" t="n">
+        <v>3</v>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>planejamento_amostragem</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>167</v>
+      </c>
+      <c r="B168" t="n">
+        <v>3</v>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>descricao_nao_conformidade</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>168</v>
+      </c>
+      <c r="B169" t="n">
+        <v>3</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>codigo_laudo_substituido</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
         <is>
           <t>sim</t>
         </is>

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -557,7 +557,7 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>versao_template</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -7210,7 +7210,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8946,7 +8946,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -9142,7 +9142,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -9786,7 +9786,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>versao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -5697,7 +5697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F169"/>
+  <dimension ref="A1:F168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9.7265625" customWidth="1" min="1" max="1"/>
@@ -10222,7 +10222,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B162" t="n">
         <v>3</v>
@@ -10234,7 +10234,7 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>coordenadas</t>
+          <t>clima_ultimas_24h</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -10250,7 +10250,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B163" t="n">
         <v>3</v>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>clima_ultimas_24h</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10278,7 +10278,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B164" t="n">
         <v>3</v>
@@ -10290,7 +10290,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>tipo_coleta</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10306,7 +10306,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B165" t="n">
         <v>3</v>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>tipo_coleta</t>
+          <t>responsavel_amostra</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10334,7 +10334,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B166" t="n">
         <v>3</v>
@@ -10346,7 +10346,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>responsavel_amostra</t>
+          <t>planejamento_amostragem</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10362,7 +10362,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B167" t="n">
         <v>3</v>
@@ -10374,7 +10374,7 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>planejamento_amostragem</t>
+          <t>descricao_nao_conformidade</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -10390,7 +10390,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B168" t="n">
         <v>3</v>
@@ -10402,7 +10402,7 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>descricao_nao_conformidade</t>
+          <t>codigo_laudo_substituido</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10411,34 +10411,6 @@
         </is>
       </c>
       <c r="F168" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="n">
-        <v>168</v>
-      </c>
-      <c r="B169" t="n">
-        <v>3</v>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="D169" t="inlineStr">
-        <is>
-          <t>codigo_laudo_substituido</t>
-        </is>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
         <is>
           <t>sim</t>
         </is>

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G143"/>
+  <dimension ref="A1:G140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Coleta:\s*(\d{2}/\d{2}/\d{4})</t>
+          <t>Data Coleta:\s*(\d{2}/\d{2}/\d{4}(?:\s+\d{2}:\d{2}(?::\d{2})?)?)</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Relatório Analítico\s*\d+/\d+\.\d+\.?([A-Z]{1,2})?</t>
+          <t>Relat.rio\s+Anal.tico(?:\s+Parcial)?\s*\d+/\d+\.\d+\.?([A-Z]{1,2})?</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1205,7 +1205,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B19" t="n">
         <v>1</v>
@@ -1217,12 +1217,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>dh_coleta</t>
+          <t>data_publicacao</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Data Coleta:\s*\d{2}/\d{2}/\d{4}\s+(\d{2}:\d{2})</t>
+          <t>Data de Publica..o:\s*(\d{2}/\d{2}/\d{4}(?:\s+\d{2}:\d{2}(?::\d{2})?)?)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1238,7 +1238,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B20" t="n">
         <v>1</v>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>data_publicacao</t>
+          <t>data_recebimento</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data de Publica..o:\s*(\d{2}/\d{2}/\d{4})</t>
+          <t>Data de Recebimento:\s*(\d{2}/\d{2}/\d{4}(?:\s+\d{2}:\d{2}(?::\d{2})?)?)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1271,7 +1271,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B21" t="n">
         <v>1</v>
@@ -1283,12 +1283,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>dh_publicacao</t>
+          <t>observacoes</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Data de Publica..o:\s*\d{2}/\d{2}/\d{4}\s+(\d{2}:\d{2})</t>
+          <t>Observa..es:\s*(.*?)(?:\s+Latitude:|\n)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1304,7 +1304,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B22" t="n">
         <v>1</v>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>data_recebimento</t>
+          <t>clima_ultimas_24h</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Data de Recebimento:\s*(\d{2}/\d{2}/\d{4})</t>
+          <t>Condi..es clim.ticas nas .ltimas 24 horas:\s*(.*?)(?:\s+Condi..es clim.ticas no momento da coleta:|\n)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1337,7 +1337,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B23" t="n">
         <v>1</v>
@@ -1349,12 +1349,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>dh_recebimento</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Data de Recebimento:\s*\d{2}/\d{2}/\d{4}\s+(\d{2}:\d{2})</t>
+          <t>Condi..es clim.ticas no momento da coleta:\s*(.*?)(?:\s+Local da Coleta:|\n)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1370,7 +1370,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B24" t="n">
         <v>1</v>
@@ -1382,12 +1382,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>observacoes</t>
+          <t>localizacao</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Observa..es:\s*(.*?)(?:\s+Latitude:|\n)</t>
+          <t>Local da Coleta:\s*(.*?)(?:\s+Tipo de Coleta:|\n)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1403,7 +1403,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B25" t="n">
         <v>1</v>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>clima_ultimas_24h</t>
+          <t>tipo_coleta</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Condi..es clim.ticas nas .ltimas 24 horas:\s*(.*?)(?:\s+Condi..es clim.ticas no momento da coleta:|\n)</t>
+          <t>Tipo de Coleta:\s*(.*?)(?:\s+Responsabilidade da Amostragem:|\n)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1436,7 +1436,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B26" t="n">
         <v>1</v>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>responsavel_amostra</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Condi..es clim.ticas no momento da coleta:\s*(.*?)(?:\s+Local da Coleta:|\n)</t>
+          <t>Responsabilidade da Amostragem:\s*(.*?)(?:\s+Descri..o|\s+Planejamento|\n)</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1469,7 +1469,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B27" t="n">
         <v>1</v>
@@ -1481,12 +1481,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>localizacao</t>
+          <t>planejamento_amostragem</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Local da Coleta:\s*(.*?)(?:\s+Tipo de Coleta:|\n)</t>
+          <t>Planejamento de Amostragem:\s*(CA\d+/\d{4})</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1502,7 +1502,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B28" t="n">
         <v>1</v>
@@ -1514,12 +1514,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>tipo_coleta</t>
+          <t>descricao_nao_conformidade</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tipo de Coleta:\s*(.*?)(?:\s+Responsabilidade da Amostragem:|\n)</t>
+          <t>Descri..o da n.o-conformidade:\s*(.*?)(?:\s+Resultados Anal.ticos|\nResultados Anal.ticos)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1535,24 +1535,24 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B29" t="n">
         <v>1</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>responsavel_amostra</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Responsabilidade da Amostragem:\s*(.*?)(?:\s+Descri..o|\s+Planejamento|\n)</t>
+          <t>DERIVADO_DO_NOME_DO_PDF</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1568,24 +1568,24 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B30" t="n">
         <v>1</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>planejamento_amostragem</t>
+          <t>proposta_comercial</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Planejamento de Amostragem:\s*(CA\d+/\d{4})</t>
+          <t>Proposta Comercial:\s*(.*?)(?:\n|\s+Identifica..o do Cliente)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1601,24 +1601,24 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B31" t="n">
         <v>1</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>descricao_nao_conformidade</t>
+          <t>cliente</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Descri..o da n.o-conformidade:\s*(.*?)(?:\s+Resultados Anal.ticos|\nResultados Anal.ticos)</t>
+          <t>Cliente:\s*(.*?)(?:\s+CNPJ/CPF:|\n)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1634,7 +1634,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B32" t="n">
         <v>1</v>
@@ -1646,12 +1646,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>cnpj_cpf</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DERIVADO_DO_NOME_DO_PDF</t>
+          <t>CNPJ/CPF:\s*([\d./-]+)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1667,7 +1667,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B33" t="n">
         <v>1</v>
@@ -1679,12 +1679,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>proposta_comercial</t>
+          <t>contato</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Proposta Comercial:\s*(.*?)(?:\n|\s+Identifica..o do Cliente)</t>
+          <t>Contato:\s*(.*?)(?:\s+Telefone:|\n)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1700,7 +1700,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B34" t="n">
         <v>1</v>
@@ -1712,12 +1712,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>cliente</t>
+          <t>telefone</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Cliente:\s*(.*?)(?:\s+CNPJ/CPF:|\n)</t>
+          <t>Telefone:\s*([\d\s()+-]+)</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1733,7 +1733,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B35" t="n">
         <v>1</v>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>cnpj_cpf</t>
+          <t>endereco</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>CNPJ/CPF:\s*([\d./-]+)</t>
+          <t>Endere..o:\s*(.*?)(?:\nInforma..es da Amostra|\n)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1766,106 +1766,100 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B36" t="n">
         <v>1</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>layout</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>contato</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Contato:\s*(.*?)(?:\s+Telefone:|\n)</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
           <t>Não se aplica</t>
         </is>
       </c>
+      <c r="F36" t="n">
+        <v>4</v>
+      </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Amostra</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B37" t="n">
         <v>1</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>layout</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>telefone</t>
+          <t>unidade</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Telefone:\s*([\d\s()+-]+)</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
           <t>Não se aplica</t>
         </is>
       </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Amostra</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B38" t="n">
         <v>1</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>layout</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>endereco</t>
+          <t>ld</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Endere..o:\s*(.*?)(?:\nInforma..es da Amostra|\n)</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
           <t>Não se aplica</t>
         </is>
       </c>
+      <c r="F38" t="n">
+        <v>2</v>
+      </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Amostra</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B39" t="n">
         <v>1</v>
@@ -1877,7 +1871,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>lq</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1886,7 +1880,7 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1896,7 +1890,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B40" t="n">
         <v>1</v>
@@ -1908,7 +1902,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>unidade</t>
+          <t>incerteza</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1917,7 +1911,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1927,7 +1921,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B41" t="n">
         <v>1</v>
@@ -1939,7 +1933,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>ld</t>
+          <t>referencia</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1948,7 +1942,7 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1958,7 +1952,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B42" t="n">
         <v>1</v>
@@ -1970,7 +1964,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>lq</t>
+          <t>data_inicio</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1979,7 +1973,7 @@
         </is>
       </c>
       <c r="F42" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1989,7 +1983,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B43" t="n">
         <v>1</v>
@@ -2001,7 +1995,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>incerteza</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2010,17 +2004,17 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Amostra</t>
+          <t>Branco</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B44" t="n">
         <v>1</v>
@@ -2032,7 +2026,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>referencia</t>
+          <t>unidade</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2041,17 +2035,17 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Amostra</t>
+          <t>Branco</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B45" t="n">
         <v>1</v>
@@ -2063,7 +2057,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>data_inicio</t>
+          <t>lq</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2072,17 +2066,17 @@
         </is>
       </c>
       <c r="F45" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Amostra</t>
+          <t>Branco</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B46" t="n">
         <v>1</v>
@@ -2094,7 +2088,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>numero_cq</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2103,7 +2097,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2113,7 +2107,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B47" t="n">
         <v>1</v>
@@ -2125,7 +2119,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>unidade</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2134,17 +2128,17 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>Duplicata</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B48" t="n">
         <v>1</v>
@@ -2156,7 +2150,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>lq</t>
+          <t>unidade</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2169,13 +2163,13 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>Duplicata</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B49" t="n">
         <v>1</v>
@@ -2200,13 +2194,13 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>Duplicata</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B50" t="n">
         <v>1</v>
@@ -2218,7 +2212,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>duplicata</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2227,7 +2221,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2237,7 +2231,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B51" t="n">
         <v>1</v>
@@ -2249,7 +2243,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>unidade</t>
+          <t>faixa_aceitacao</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2258,7 +2252,7 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2268,7 +2262,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B52" t="n">
         <v>1</v>
@@ -2280,7 +2274,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>numero_cq</t>
+          <t>variacao_percentual</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2289,7 +2283,7 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2299,7 +2293,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B53" t="n">
         <v>1</v>
@@ -2311,7 +2305,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>duplicata</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2320,17 +2314,17 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Recuperacao</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B54" t="n">
         <v>1</v>
@@ -2342,7 +2336,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>faixa_aceitacao</t>
+          <t>unidade</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2351,17 +2345,17 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Recuperacao</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B55" t="n">
         <v>1</v>
@@ -2373,7 +2367,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>variacao_percentual</t>
+          <t>numero_cq</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2382,17 +2376,17 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Recuperacao</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B56" t="n">
         <v>1</v>
@@ -2404,7 +2398,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>faixa_aceitacao</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2413,7 +2407,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2423,7 +2417,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B57" t="n">
         <v>1</v>
@@ -2435,7 +2429,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>unidade</t>
+          <t>quantidade_adicionada</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2444,7 +2438,7 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2454,7 +2448,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B58" t="n">
         <v>1</v>
@@ -2466,7 +2460,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>numero_cq</t>
+          <t>recuperacao_percentual</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2475,7 +2469,7 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2485,100 +2479,106 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B59" t="n">
         <v>1</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>layout</t>
+          <t>header_alias</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>faixa_aceitacao</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>4</v>
+          <t>^(analise|parametros?)$</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Não aplicável</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Recuperacao</t>
+          <t>Não aplicável</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B60" t="n">
         <v>1</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>layout</t>
+          <t>header_alias</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>quantidade_adicionada</t>
+          <t>unidade</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>2</v>
+          <t>^(unidade|unid)$</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Não aplicável</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Recuperacao</t>
+          <t>Não aplicável</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B61" t="n">
         <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>layout</t>
+          <t>header_alias</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>recuperacao_percentual</t>
+          <t>ld</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>5</v>
+          <t>(^ld$|limite\s+de\s+deteccao)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Não aplicável</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Recuperacao</t>
+          <t>Não aplicável</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B62" t="n">
         <v>1</v>
@@ -2590,12 +2590,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>lq</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>^(analise|parametros?)$</t>
+          <t>(^lq$|limite\s+de\s+quantificacao)</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2611,7 +2611,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B63" t="n">
         <v>1</v>
@@ -2623,12 +2623,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>unidade</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>^(unidade|unid)$</t>
+          <t>^resultados?$</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2644,7 +2644,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B64" t="n">
         <v>1</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>ld</t>
+          <t>incerteza</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>(^ld$|limite\s+de\s+deteccao)</t>
+          <t>incerteza</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2677,7 +2677,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B65" t="n">
         <v>1</v>
@@ -2689,12 +2689,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>lq</t>
+          <t>referencia</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>(^lq$|limite\s+de\s+quantificacao)</t>
+          <t>referencia</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2710,7 +2710,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B66" t="n">
         <v>1</v>
@@ -2722,12 +2722,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>data_inicio</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>^resultados?$</t>
+          <t>data\s+de\s+inicio|data\s+inicio</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2743,7 +2743,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B67" t="n">
         <v>1</v>
@@ -2755,12 +2755,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>incerteza</t>
+          <t>numero_cq</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>incerteza</t>
+          <t>numero\s+do\s+cq|^cq$</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2776,7 +2776,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B68" t="n">
         <v>1</v>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>referencia</t>
+          <t>duplicata</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>referencia</t>
+          <t>^duplicata$</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2809,7 +2809,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B69" t="n">
         <v>1</v>
@@ -2821,12 +2821,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>data_inicio</t>
+          <t>faixa_aceitacao</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>data\s+de\s+inicio|data\s+inicio</t>
+          <t>faixa\s+de\s+aceitacao</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2842,7 +2842,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B70" t="n">
         <v>1</v>
@@ -2854,12 +2854,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>numero_cq</t>
+          <t>variacao_percentual</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>numero\s+do\s+cq|^cq$</t>
+          <t>variacao</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2875,7 +2875,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B71" t="n">
         <v>1</v>
@@ -2887,12 +2887,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>duplicata</t>
+          <t>quantidade_adicionada</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>^duplicata$</t>
+          <t>quantidade\s+adicionada|^qtd\s+adicionada$</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2908,7 +2908,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B72" t="n">
         <v>1</v>
@@ -2920,12 +2920,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>faixa_aceitacao</t>
+          <t>recuperacao_percentual</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>faixa\s+de\s+aceitacao</t>
+          <t>recuperacao</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2941,7 +2941,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B73" t="n">
         <v>1</v>
@@ -2953,12 +2953,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>variacao_percentual</t>
+          <t>conama</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>variacao</t>
+          <t>conama</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2974,7 +2974,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B74" t="n">
         <v>1</v>
@@ -2986,12 +2986,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>quantidade_adicionada</t>
+          <t>copam_cerh</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>quantidade\s+adicionada|^qtd\s+adicionada$</t>
+          <t>copam|cerh|deliberacao\s+normativa</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3007,106 +3007,106 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B75" t="n">
         <v>1</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>header_alias</t>
+          <t>category_type</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>recuperacao_percentual</t>
+          <t>Controle de Qualidade</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>recuperacao</t>
+          <t>controle\ de\ qualidade</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>categoria=Controle de Qualidade; subcategoria=Não aplicável; local=Não aplicável; prioridade=Não aplicável; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>Amostra</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B76" t="n">
         <v>1</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>header_alias</t>
+          <t>category_type</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>conama</t>
+          <t>Controle de Qualidade</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>conama</t>
+          <t>branco\ \-\ físico\-químico\.parâmetros</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>categoria=Controle de Qualidade; subcategoria=Não aplicável; local=Não aplicável; prioridade=Não aplicável; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>Branco</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B77" t="n">
         <v>1</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>header_alias</t>
+          <t>category_type</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>copam_cerh</t>
+          <t>Controle de Qualidade</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>copam|cerh|deliberacao\s+normativa</t>
+          <t>branco\ \-\ físico\-químico\.número\ do\ cq</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>categoria=Controle de Qualidade; subcategoria=Não aplicável; local=Não aplicável; prioridade=Não aplicável; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>Branco</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B78" t="n">
         <v>1</v>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>controle\ de\ qualidade</t>
+          <t>branco\ \-\ físico\-químico\.resultado</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3133,13 +3133,13 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Amostra</t>
+          <t>Branco</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B79" t="n">
         <v>1</v>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>branco\ \-\ físico\-químico\.parâmetros</t>
+          <t>branco\ \-\ físico\-químico\.unidade</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3172,7 +3172,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B80" t="n">
         <v>1</v>
@@ -3189,7 +3189,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>branco\ \-\ físico\-químico\.número\ do\ cq</t>
+          <t>branco\ \-\ físico\-químico\.limite\ de\ quantificação</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3205,7 +3205,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B81" t="n">
         <v>1</v>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>branco\ \-\ físico\-químico\.resultado</t>
+          <t>branco\ \-\ metais\.parâmetros</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3238,7 +3238,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B82" t="n">
         <v>1</v>
@@ -3255,7 +3255,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>branco\ \-\ físico\-químico\.unidade</t>
+          <t>branco\ \-\ metais\.número\ do\ cq</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3271,7 +3271,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B83" t="n">
         <v>1</v>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>branco\ \-\ físico\-químico\.limite\ de\ quantificação</t>
+          <t>branco\ \-\ metais\.resultado</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3304,7 +3304,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B84" t="n">
         <v>1</v>
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>branco\ \-\ metais\.parâmetros</t>
+          <t>branco\ \-\ metais\.unidade</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3337,7 +3337,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B85" t="n">
         <v>1</v>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>branco\ \-\ metais\.número\ do\ cq</t>
+          <t>branco\ \-\ metais\.limite\ de\ quantificação</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3370,7 +3370,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B86" t="n">
         <v>1</v>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>branco\ \-\ metais\.resultado</t>
+          <t>branco\ \-\ microbiológicos\.parâmetros</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3403,7 +3403,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B87" t="n">
         <v>1</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>branco\ \-\ metais\.unidade</t>
+          <t>branco\ \-\ microbiológicos\.número\ do\ cq</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3436,7 +3436,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B88" t="n">
         <v>1</v>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>branco\ \-\ metais\.limite\ de\ quantificação</t>
+          <t>branco\ \-\ microbiológicos\.resultado</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3469,7 +3469,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B89" t="n">
         <v>1</v>
@@ -3486,7 +3486,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>branco\ \-\ microbiológicos\.parâmetros</t>
+          <t>branco\ \-\ microbiológicos\.unidade</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3502,7 +3502,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B90" t="n">
         <v>1</v>
@@ -3519,7 +3519,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>branco\ \-\ microbiológicos\.número\ do\ cq</t>
+          <t>branco\ \-\ microbiológicos\.limite\ de\ quantificação</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3535,7 +3535,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B91" t="n">
         <v>1</v>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>branco\ \-\ microbiológicos\.resultado</t>
+          <t>duplicata\ \-\ físico\-químico\.parâmetros</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3562,13 +3562,13 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>Duplicata</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B92" t="n">
         <v>1</v>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>branco\ \-\ microbiológicos\.unidade</t>
+          <t>duplicata\ \-\ físico\-químico\.número\ do\ cq</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3595,13 +3595,13 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>Duplicata</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B93" t="n">
         <v>1</v>
@@ -3618,7 +3618,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>branco\ \-\ microbiológicos\.limite\ de\ quantificação</t>
+          <t>duplicata\ \-\ físico\-químico\.resultado</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3628,13 +3628,13 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>Duplicata</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B94" t="n">
         <v>1</v>
@@ -3651,7 +3651,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ físico\-químico\.parâmetros</t>
+          <t>duplicata\ \-\ físico\-químico\.duplicata</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3667,7 +3667,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B95" t="n">
         <v>1</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ físico\-químico\.número\ do\ cq</t>
+          <t>duplicata\ \-\ físico\-químico\.unidade</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3700,7 +3700,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B96" t="n">
         <v>1</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ físico\-químico\.resultado</t>
+          <t>duplicata\ \-\ físico\-químico\.faixa\ de\ aceitação</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3733,7 +3733,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B97" t="n">
         <v>1</v>
@@ -3750,7 +3750,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ físico\-químico\.duplicata</t>
+          <t>duplicata\ \-\ físico\-químico\.variação\ \(%\)</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3766,7 +3766,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B98" t="n">
         <v>1</v>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ físico\-químico\.unidade</t>
+          <t>duplicata\ \-\ metais\.parâmetros</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3799,7 +3799,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B99" t="n">
         <v>1</v>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ físico\-químico\.faixa\ de\ aceitação</t>
+          <t>duplicata\ \-\ metais\.número\ do\ cq</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3832,7 +3832,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B100" t="n">
         <v>1</v>
@@ -3849,7 +3849,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ físico\-químico\.variação\ \(%\)</t>
+          <t>duplicata\ \-\ metais\.resultado</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3865,7 +3865,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B101" t="n">
         <v>1</v>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ metais\.parâmetros</t>
+          <t>duplicata\ \-\ metais\.duplicata</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3898,7 +3898,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B102" t="n">
         <v>1</v>
@@ -3915,7 +3915,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ metais\.número\ do\ cq</t>
+          <t>duplicata\ \-\ metais\.unidade</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3931,7 +3931,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B103" t="n">
         <v>1</v>
@@ -3948,7 +3948,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ metais\.resultado</t>
+          <t>duplicata\ \-\ metais\.faixa\ de\ aceitação</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3964,7 +3964,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B104" t="n">
         <v>1</v>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ metais\.duplicata</t>
+          <t>duplicata\ \-\ metais\.variação\ \(%\)</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3997,7 +3997,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B105" t="n">
         <v>1</v>
@@ -4014,7 +4014,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ metais\.unidade</t>
+          <t>duplicata\ \-\ microbiológicos\.parâmetros</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4030,7 +4030,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B106" t="n">
         <v>1</v>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ metais\.faixa\ de\ aceitação</t>
+          <t>duplicata\ \-\ microbiológicos\.número\ do\ cq</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4063,7 +4063,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B107" t="n">
         <v>1</v>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ metais\.variação\ \(%\)</t>
+          <t>duplicata\ \-\ microbiológicos\.resultado</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4096,7 +4096,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B108" t="n">
         <v>1</v>
@@ -4113,7 +4113,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ microbiológicos\.parâmetros</t>
+          <t>duplicata\ \-\ microbiológicos\.duplicata</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4129,7 +4129,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B109" t="n">
         <v>1</v>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ microbiológicos\.número\ do\ cq</t>
+          <t>duplicata\ \-\ microbiológicos\.unidade</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4162,7 +4162,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B110" t="n">
         <v>1</v>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ microbiológicos\.resultado</t>
+          <t>duplicata\ \-\ microbiológicos\.faixa\ de\ aceitação</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4195,7 +4195,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B111" t="n">
         <v>1</v>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ microbiológicos\.duplicata</t>
+          <t>duplicata\ \-\ microbiológicos\.variação\ \(%\)</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4228,47 +4228,47 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="B112" t="n">
         <v>1</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>category_type</t>
+          <t>category_alias</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Controle de Qualidade</t>
+          <t>Resultados Analíticos</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ microbiológicos\.unidade</t>
+          <t>^resultados\s+analiticos</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>categoria=Controle de Qualidade; subcategoria=Não aplicável; local=Não aplicável; prioridade=Não aplicável; extrair_subcategoria=Falso</t>
+          <t>categoria=Resultados Analíticos; subcategoria=Não aplicável; local=laboratorio; prioridade=Não aplicável; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Não aplicável</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B113" t="n">
         <v>1</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>category_type</t>
+          <t>category_alias</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4278,155 +4278,155 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ microbiológicos\.faixa\ de\ aceitação</t>
+          <t>^controle\s+de\s+qualidade</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>categoria=Controle de Qualidade; subcategoria=Não aplicável; local=Não aplicável; prioridade=Não aplicável; extrair_subcategoria=Falso</t>
+          <t>categoria=Controle de Qualidade; subcategoria=Não aplicável; local=laboratorio; prioridade=Não aplicável; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Não aplicável</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B114" t="n">
         <v>1</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>category_type</t>
+          <t>category_alias</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Controle de Qualidade</t>
+          <t>Provedores Externos</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>duplicata\ \-\ microbiológicos\.variação\ \(%\)</t>
+          <t>^(provedores?\s+externos?|ethica\s+ambiental)</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>categoria=Controle de Qualidade; subcategoria=Não aplicável; local=Não aplicável; prioridade=Não aplicável; extrair_subcategoria=Falso</t>
+          <t>categoria=Provedores Externos; subcategoria=Não aplicável; local=laboratorio; prioridade=Não aplicável; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Não aplicável</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B115" t="n">
         <v>1</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>category_alias</t>
+          <t>subcategory_alias</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Resultados Analíticos</t>
+          <t>Amostragem</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>^resultados\s+analiticos</t>
+          <t>^amostragem$</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>categoria=Resultados Analíticos; subcategoria=Não aplicável; local=laboratorio; prioridade=Não aplicável; extrair_subcategoria=Falso</t>
+          <t>categoria=Resultados Analíticos; subcategoria=Amostragem; local=campo; prioridade=10; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>Amostra</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B116" t="n">
         <v>1</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>category_alias</t>
+          <t>subcategory_alias</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Controle de Qualidade</t>
+          <t>Físico-Químico</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>^controle\s+de\s+qualidade</t>
+          <t>^fisico[- ]quimico$</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>categoria=Controle de Qualidade; subcategoria=Não aplicável; local=laboratorio; prioridade=Não aplicável; extrair_subcategoria=Falso</t>
+          <t>categoria=Resultados Analíticos; subcategoria=Físico-Químico; local=laboratorio; prioridade=20; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>Amostra</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B117" t="n">
         <v>1</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>category_alias</t>
+          <t>subcategory_alias</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Provedores Externos</t>
+          <t>Constituintes inorgânicos não metálicos</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>^(provedores?\s+externos?|ethica\s+ambiental)</t>
+          <t>^constituintes\s+inorganicos\s+nao\s+metalicos$</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>categoria=Provedores Externos; subcategoria=Não aplicável; local=laboratorio; prioridade=Não aplicável; extrair_subcategoria=Falso</t>
+          <t>categoria=Resultados Analíticos; subcategoria=Constituintes inorgânicos não metálicos; local=laboratorio; prioridade=30; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>Amostra</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B118" t="n">
         <v>1</v>
@@ -4438,17 +4438,17 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Amostragem</t>
+          <t>Constituintes orgânicos agregados</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>^amostragem$</t>
+          <t>^constituintes\s+organicos\s+agregados$</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>categoria=Resultados Analíticos; subcategoria=Amostragem; local=campo; prioridade=10; extrair_subcategoria=Falso</t>
+          <t>categoria=Resultados Analíticos; subcategoria=Constituintes orgânicos agregados; local=laboratorio; prioridade=40; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -4459,7 +4459,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B119" t="n">
         <v>1</v>
@@ -4471,17 +4471,17 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Físico-Químico</t>
+          <t>Metais</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>^fisico[- ]quimico$</t>
+          <t>^metais$</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>categoria=Resultados Analíticos; subcategoria=Físico-Químico; local=laboratorio; prioridade=20; extrair_subcategoria=Falso</t>
+          <t>categoria=Resultados Analíticos; subcategoria=Metais; local=laboratorio; prioridade=50; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4492,7 +4492,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="B120" t="n">
         <v>1</v>
@@ -4504,17 +4504,17 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Constituintes inorgânicos não metálicos</t>
+          <t>Microbiológicos</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>^constituintes\s+inorganicos\s+nao\s+metalicos$</t>
+          <t>^microbiologicos$</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>categoria=Resultados Analíticos; subcategoria=Constituintes inorgânicos não metálicos; local=laboratorio; prioridade=30; extrair_subcategoria=Falso</t>
+          <t>categoria=Resultados Analíticos; subcategoria=Microbiológicos; local=laboratorio; prioridade=60; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -4525,7 +4525,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B121" t="n">
         <v>1</v>
@@ -4537,17 +4537,17 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Constituintes orgânicos agregados</t>
+          <t>Propriedades físicas e agregadas</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>^constituintes\s+organicos\s+agregados$</t>
+          <t>^propriedades\s+fisicas\s+e\s+agregadas$</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>categoria=Resultados Analíticos; subcategoria=Constituintes orgânicos agregados; local=laboratorio; prioridade=40; extrair_subcategoria=Falso</t>
+          <t>categoria=Resultados Analíticos; subcategoria=Propriedades físicas e agregadas; local=laboratorio; prioridade=70; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
@@ -4558,7 +4558,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="B122" t="n">
         <v>1</v>
@@ -4570,17 +4570,17 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Metais</t>
+          <t>Compostos orgânicos semi-voláteis</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>^metais$</t>
+          <t>^compostos\s+organicos\s+semi[- ]volateis$</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>categoria=Resultados Analíticos; subcategoria=Metais; local=laboratorio; prioridade=50; extrair_subcategoria=Falso</t>
+          <t>categoria=Resultados Analíticos; subcategoria=Compostos orgânicos semi-voláteis; local=laboratorio; prioridade=80; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -4591,7 +4591,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="B123" t="n">
         <v>1</v>
@@ -4603,17 +4603,17 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Microbiológicos</t>
+          <t>Cromatografia</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>^microbiologicos$</t>
+          <t>^cromatografia$</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>categoria=Resultados Analíticos; subcategoria=Microbiológicos; local=laboratorio; prioridade=60; extrair_subcategoria=Falso</t>
+          <t>categoria=Resultados Analíticos; subcategoria=Cromatografia; local=laboratorio; prioridade=90; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -4624,7 +4624,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="B124" t="n">
         <v>1</v>
@@ -4636,17 +4636,17 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Propriedades físicas e agregadas</t>
+          <t>Ethica Ambiental</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>^propriedades\s+fisicas\s+e\s+agregadas$</t>
+          <t>^ethica\s+ambiental.*</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>categoria=Resultados Analíticos; subcategoria=Propriedades físicas e agregadas; local=laboratorio; prioridade=70; extrair_subcategoria=Falso</t>
+          <t>categoria=Provedores Externos; subcategoria=Ethica Ambiental; local=laboratorio; prioridade=200; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
@@ -4657,7 +4657,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B125" t="n">
         <v>1</v>
@@ -4669,28 +4669,28 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Compostos orgânicos semi-voláteis</t>
+          <t>Não aplicável</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>^compostos\s+organicos\s+semi[- ]volateis$</t>
+          <t>^branco\s+-\s+.+</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>categoria=Resultados Analíticos; subcategoria=Compostos orgânicos semi-voláteis; local=laboratorio; prioridade=80; extrair_subcategoria=Falso</t>
+          <t>categoria=Controle de Qualidade; subcategoria=Não aplicável; local=laboratorio; prioridade=300; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Amostra</t>
+          <t>Branco</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="B126" t="n">
         <v>1</v>
@@ -4702,28 +4702,28 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Cromatografia</t>
+          <t>Não aplicável</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>^cromatografia$</t>
+          <t>^duplicata\s+-\s+.+</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>categoria=Resultados Analíticos; subcategoria=Cromatografia; local=laboratorio; prioridade=90; extrair_subcategoria=Falso</t>
+          <t>categoria=Controle de Qualidade; subcategoria=Não aplicável; local=laboratorio; prioridade=310; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Amostra</t>
+          <t>Duplicata</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="B127" t="n">
         <v>1</v>
@@ -4735,50 +4735,50 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Ethica Ambiental</t>
+          <t>Não aplicável</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>^ethica\s+ambiental.*</t>
+          <t>^recuperacao\s+-\s+.+</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>categoria=Provedores Externos; subcategoria=Ethica Ambiental; local=laboratorio; prioridade=200; extrair_subcategoria=Falso</t>
+          <t>categoria=Controle de Qualidade; subcategoria=Não aplicável; local=laboratorio; prioridade=320; extrair_subcategoria=Falso</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Amostra</t>
+          <t>Recuperacao</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="B128" t="n">
         <v>1</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>subcategory_alias</t>
+          <t>continuation</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>continuidade_tabela</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>^branco\s+-\s+.+</t>
+          <t>\bCQ\d+</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>categoria=Controle de Qualidade; subcategoria=Não aplicável; local=laboratorio; prioridade=300; extrair_subcategoria=Falso</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -4789,29 +4789,29 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B129" t="n">
         <v>1</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>subcategory_alias</t>
+          <t>continuation</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>continuidade_tabela</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>^duplicata\s+-\s+.+</t>
+          <t>\bCQ\d+</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>categoria=Controle de Qualidade; subcategoria=Não aplicável; local=laboratorio; prioridade=310; extrair_subcategoria=Falso</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -4822,29 +4822,29 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="B130" t="n">
         <v>1</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>subcategory_alias</t>
+          <t>continuation</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Não aplicável</t>
+          <t>continuidade_tabela</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>^recuperacao\s+-\s+.+</t>
+          <t>\bCQ\d+</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>categoria=Controle de Qualidade; subcategoria=Não aplicável; local=laboratorio; prioridade=320; extrair_subcategoria=Falso</t>
+          <t>Não se aplica</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
@@ -4855,128 +4855,128 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="B131" t="n">
         <v>1</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>continuation</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>continuidade_tabela</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>\bCQ\d+</t>
+          <t>Informa..es da Amostra\s*-\s*N.?\s*:\s*(.*?)(?:\s+Tipo de Amostra:|\n)</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>Nao se aplica</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Branco</t>
+          <t>Nao se aplica</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B132" t="n">
         <v>1</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>continuation</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>continuidade_tabela</t>
+          <t>section_start</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>\bCQ\d+</t>
+          <t>Embalagens\s+e\s+Preservantes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>descricao=Identifica o inicio da secao de Embalagens e Preservantes.</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Duplicata</t>
+          <t>Nao se aplica</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="B133" t="n">
         <v>1</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>continuation</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>continuidade_tabela</t>
+          <t>table_header</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>\bCQ\d+</t>
+          <t>\bEmbalagem\b\s+\bVolume\b\s+Preserva..o\s+M.todos</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Não se aplica</t>
+          <t>descricao=Identifica o cabecalho da tabela de embalagens e preservantes.</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Recuperacao</t>
+          <t>Nao se aplica</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="B134" t="n">
         <v>1</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>sample_identification</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Informa..es da Amostra\s*-\s*N.?\s*:\s*(.*?)(?:\s+Tipo de Amostra:|\n)</t>
+          <t>^\s*\d+\s*-\s*.+$</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Nao se aplica</t>
+          <t>descricao=Identifica a linha da amostra associada ao quadro.</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -4987,128 +4987,128 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="B135" t="n">
         <v>1</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>section_start</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Embalagens\s+e\s+Preservantes</t>
+          <t>(?:^|\n)\s*Notas?\s*:?\s*(.*?)(?=\n\s*(?:Considera..es\s+Gerais|Declara..o\s+de\s+Conformidade|Chave\s+de\s+Valida..o|$))</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>descricao=Identifica o inicio da secao de Embalagens e Preservantes.</t>
+          <t>descricao=Extrai o bloco textual de Notas.</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Nao se aplica</t>
+          <t>N?o se aplica</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B136" t="n">
         <v>1</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>table_header</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>\bEmbalagem\b\s+\bVolume\b\s+Preserva..o\s+M.todos</t>
+          <t>(?:^|\n)\s*Considera..es\s+Gerais\s*:?\s*(.*?)(?=\n\s*(?:Declara..o\s+de\s+Conformidade|Chave\s+de\s+Valida..o|Notas?|$))</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>descricao=Identifica o cabecalho da tabela de embalagens e preservantes.</t>
+          <t>descricao=Extrai o bloco textual de Consideracoes Gerais.</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Nao se aplica</t>
+          <t>N?o se aplica</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B137" t="n">
         <v>1</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>sample_identification</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>^\s*\d+\s*-\s*.+$</t>
+          <t>(?:^|\n)\s*Declara..o\s+de\s+Conformidade\s*:?\s*(.*?)(?=\n\s*(?:Chave\s+de\s+Valida..o|Considera..es\s+Gerais|Notas?|$))</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>descricao=Identifica a linha da amostra associada ao quadro.</t>
+          <t>descricao=Extrai o bloco textual de Declaracao de Conformidade.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Nao se aplica</t>
+          <t>N?o se aplica</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="B138" t="n">
         <v>1</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>chave_validacao</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>(?:^|\n)\s*Notas?\s*:?\s*(.*?)(?=\n\s*(?:Considera..es\s+Gerais|Declara..o\s+de\s+Conformidade|Chave\s+de\s+Valida..o|$))</t>
+          <t>(?:^|\n)\s*Chave\s+de\s+Valida..o\s*:?\s*((?!FO-ANL-\d+\b)[A-Za-z0-9][A-Za-z0-9\-_.]{7,})</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>descricao=Extrai o bloco textual de Notas.</t>
+          <t>descricao=Extrai a chave de validacao do laudo.</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -5119,29 +5119,29 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="B139" t="n">
         <v>1</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>codigo_laudo</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>(?:^|\n)\s*Considera..es\s+Gerais\s*:?\s*(.*?)(?=\n\s*(?:Declara..o\s+de\s+Conformidade|Chave\s+de\s+Valida..o|Notas?|$))</t>
+          <t>(Relat.rio\s+Anal.tico(?:\s+Parcial)?\s*\d+/\d+\.\d+(?:\.[A-Z]{1,2})?)</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>descricao=Extrai o bloco textual de Consideracoes Gerais.</t>
+          <t>N?o se aplica</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -5152,131 +5152,32 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B140" t="n">
         <v>1</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>codigo_laudo_substituido</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>(?:^|\n)\s*Declara..o\s+de\s+Conformidade\s*:?\s*(.*?)(?=\n\s*(?:Chave\s+de\s+Valida..o|Considera..es\s+Gerais|Notas?|$))</t>
+          <t>(Este\s+relat.rio\s+anal.tico\s+cancela\s+e\s+substitui\s+o\s+relat.rio\s+\d+/\d+\.\d+)</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>descricao=Extrai o bloco textual de Declaracao de Conformidade.</t>
+          <t>N?o se aplica</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
-        <is>
-          <t>N?o se aplica</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>140</v>
-      </c>
-      <c r="B141" t="n">
-        <v>1</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>validation_key</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>chave_validacao</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>(?:^|\n)\s*Chave\s+de\s+Valida..o\s*:?\s*((?!FO-ANL-\d+\b)[A-Za-z0-9][A-Za-z0-9\-_.]{7,})</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>descricao=Extrai a chave de validacao do laudo.</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>N?o se aplica</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>141</v>
-      </c>
-      <c r="B142" t="n">
-        <v>1</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>metadata</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>codigo_laudo</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>(Relat.rio Anal.tico\s*\d+/\d+\.\d+(?:\.[A-Z]{1,2})?)</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>N?o se aplica</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>N?o se aplica</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" t="n">
-        <v>1</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>sample</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>codigo_laudo_substituido</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>(Este\s+relat.rio\s+anal.tico\s+cancela\s+e\s+substitui\s+o\s+relat.rio\s+\d+/\d+\.\d+)</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>N?o se aplica</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
         <is>
           <t>N?o se aplica</t>
         </is>
@@ -5697,7 +5598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F168"/>
+  <dimension ref="A1:F193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9.7265625" customWidth="1" min="1" max="1"/>
@@ -5742,24 +5643,24 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>83</v>
       </c>
       <c r="B2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>results_extract</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -5770,24 +5671,24 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
+        <v>84</v>
+      </c>
+      <c r="B3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
-        <v>4</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>results_extract</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -5798,24 +5699,24 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3</v>
+        <v>85</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>results_extract</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -5826,24 +5727,24 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>4</v>
+        <v>86</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>results_extract</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>data_coleta</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -5854,24 +5755,24 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>5</v>
+        <v>87</v>
       </c>
       <c r="B6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>results_extract</t>
+          <t>metadata</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>subtipo_amostra</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -5882,7 +5783,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="B7" t="n">
         <v>4</v>
@@ -5894,7 +5795,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>tipo</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -5910,7 +5811,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="B8" t="n">
         <v>4</v>
@@ -5922,12 +5823,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>categoria</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -5938,7 +5839,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="B9" t="n">
         <v>4</v>
@@ -5950,7 +5851,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>subcategoria</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5966,7 +5867,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="B10" t="n">
         <v>4</v>
@@ -5978,12 +5879,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>codigo_laudo</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -5994,7 +5895,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10</v>
+        <v>92</v>
       </c>
       <c r="B11" t="n">
         <v>4</v>
@@ -6006,12 +5907,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>codigo_laudo_substituido</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -6022,7 +5923,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="B12" t="n">
         <v>4</v>
@@ -6034,12 +5935,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -6050,7 +5951,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="B13" t="n">
         <v>4</v>
@@ -6062,7 +5963,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>tipo</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6078,7 +5979,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>13</v>
+        <v>95</v>
       </c>
       <c r="B14" t="n">
         <v>4</v>
@@ -6090,12 +5991,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>acm_resultado_tratado</t>
+          <t>categoria</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -6106,7 +6007,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>14</v>
+        <v>96</v>
       </c>
       <c r="B15" t="n">
         <v>4</v>
@@ -6118,7 +6019,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>acm_qualificador</t>
+          <t>subcategoria</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6134,7 +6035,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>15</v>
+        <v>97</v>
       </c>
       <c r="B16" t="n">
         <v>4</v>
@@ -6146,7 +6047,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>acm_unidade</t>
+          <t>codigo_laudo</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6162,7 +6063,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>16</v>
+        <v>98</v>
       </c>
       <c r="B17" t="n">
         <v>4</v>
@@ -6174,7 +6075,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>codigo_laudo_substituido</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6190,7 +6091,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>17</v>
+        <v>99</v>
       </c>
       <c r="B18" t="n">
         <v>4</v>
@@ -6202,12 +6103,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>data_inicio</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -6218,7 +6119,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="B19" t="n">
         <v>4</v>
@@ -6230,7 +6131,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>conama</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6246,7 +6147,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="B20" t="n">
         <v>4</v>
@@ -6258,12 +6159,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>acm_conama_operador</t>
+          <t>acm_resultado_tratado</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -6274,7 +6175,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="B21" t="n">
         <v>4</v>
@@ -6286,12 +6187,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>acm_conama_minimo</t>
+          <t>acm_qualificador</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -6302,7 +6203,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="B22" t="n">
         <v>4</v>
@@ -6314,12 +6215,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>acm_conama_maximo</t>
+          <t>acm_unidade</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6330,7 +6231,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>22</v>
+        <v>104</v>
       </c>
       <c r="B23" t="n">
         <v>4</v>
@@ -6342,7 +6243,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>acm_conama_unidade</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -6358,7 +6259,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>23</v>
+        <v>105</v>
       </c>
       <c r="B24" t="n">
         <v>4</v>
@@ -6370,12 +6271,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>copam_cerh</t>
+          <t>data_inicio</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -6386,7 +6287,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="B25" t="n">
         <v>4</v>
@@ -6398,7 +6299,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_operador</t>
+          <t>conama</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -6414,7 +6315,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>25</v>
+        <v>107</v>
       </c>
       <c r="B26" t="n">
         <v>4</v>
@@ -6426,12 +6327,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_minimo</t>
+          <t>acm_conama_operador</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -6442,7 +6343,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>26</v>
+        <v>108</v>
       </c>
       <c r="B27" t="n">
         <v>4</v>
@@ -6454,7 +6355,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_maximo</t>
+          <t>acm_conama_minimo</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -6470,7 +6371,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>27</v>
+        <v>109</v>
       </c>
       <c r="B28" t="n">
         <v>4</v>
@@ -6482,12 +6383,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_unidade</t>
+          <t>acm_conama_maximo</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -6498,7 +6399,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>28</v>
+        <v>110</v>
       </c>
       <c r="B29" t="n">
         <v>4</v>
@@ -6510,7 +6411,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>ld</t>
+          <t>acm_conama_unidade</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -6526,7 +6427,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>29</v>
+        <v>111</v>
       </c>
       <c r="B30" t="n">
         <v>4</v>
@@ -6538,12 +6439,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>acm_ld_minimo</t>
+          <t>copam_cerh</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6554,7 +6455,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="B31" t="n">
         <v>4</v>
@@ -6566,12 +6467,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>acm_ld_maximo</t>
+          <t>acm_copam_cerh_operador</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6582,7 +6483,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>31</v>
+        <v>113</v>
       </c>
       <c r="B32" t="n">
         <v>4</v>
@@ -6594,12 +6495,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>acm_ld_unidade</t>
+          <t>acm_copam_cerh_minimo</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6610,7 +6511,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>32</v>
+        <v>114</v>
       </c>
       <c r="B33" t="n">
         <v>4</v>
@@ -6622,12 +6523,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>lq</t>
+          <t>acm_copam_cerh_maximo</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6638,7 +6539,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>33</v>
+        <v>115</v>
       </c>
       <c r="B34" t="n">
         <v>4</v>
@@ -6650,12 +6551,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>acm_lq_minimo</t>
+          <t>acm_copam_cerh_unidade</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6666,7 +6567,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>34</v>
+        <v>116</v>
       </c>
       <c r="B35" t="n">
         <v>4</v>
@@ -6678,12 +6579,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>acm_lq_maximo</t>
+          <t>ld</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6694,7 +6595,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="B36" t="n">
         <v>4</v>
@@ -6706,12 +6607,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>acm_lq_unidade</t>
+          <t>acm_ld_minimo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6722,7 +6623,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="B37" t="n">
         <v>4</v>
@@ -6734,12 +6635,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>referencia</t>
+          <t>acm_ld_maximo</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -6750,7 +6651,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="B38" t="n">
         <v>4</v>
@@ -6762,7 +6663,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>incerteza</t>
+          <t>acm_ld_unidade</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -6778,7 +6679,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="B39" t="n">
         <v>4</v>
@@ -6790,12 +6691,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>acm_incerteza_valor</t>
+          <t>lq</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -6806,7 +6707,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="B40" t="n">
         <v>4</v>
@@ -6818,12 +6719,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>acm_incerteza_unidade</t>
+          <t>acm_lq_minimo</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -6834,7 +6735,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>40</v>
+        <v>122</v>
       </c>
       <c r="B41" t="n">
         <v>4</v>
@@ -6846,12 +6747,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>numero_cq</t>
+          <t>acm_lq_maximo</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -6862,7 +6763,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="B42" t="n">
         <v>4</v>
@@ -6874,12 +6775,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>duplicata</t>
+          <t>acm_lq_unidade</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>texto_numerico</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -6890,7 +6791,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>42</v>
+        <v>124</v>
       </c>
       <c r="B43" t="n">
         <v>4</v>
@@ -6902,7 +6803,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>faixa_aceitacao</t>
+          <t>referencia</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6918,7 +6819,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>43</v>
+        <v>125</v>
       </c>
       <c r="B44" t="n">
         <v>4</v>
@@ -6930,7 +6831,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_operador</t>
+          <t>incerteza</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6946,7 +6847,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>44</v>
+        <v>126</v>
       </c>
       <c r="B45" t="n">
         <v>4</v>
@@ -6958,7 +6859,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_minimo</t>
+          <t>acm_incerteza_valor</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6974,7 +6875,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>45</v>
+        <v>127</v>
       </c>
       <c r="B46" t="n">
         <v>4</v>
@@ -6986,12 +6887,12 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_maximo</t>
+          <t>acm_incerteza_unidade</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -7002,7 +6903,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>46</v>
+        <v>128</v>
       </c>
       <c r="B47" t="n">
         <v>4</v>
@@ -7014,7 +6915,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_unidade</t>
+          <t>numero_cq</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -7030,7 +6931,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>47</v>
+        <v>129</v>
       </c>
       <c r="B48" t="n">
         <v>4</v>
@@ -7042,12 +6943,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>variacao_percentual</t>
+          <t>duplicata</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto_numerico</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -7058,7 +6959,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>48</v>
+        <v>130</v>
       </c>
       <c r="B49" t="n">
         <v>4</v>
@@ -7070,12 +6971,12 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>quantidade_adicionada</t>
+          <t>faixa_aceitacao</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -7086,7 +6987,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>49</v>
+        <v>131</v>
       </c>
       <c r="B50" t="n">
         <v>4</v>
@@ -7098,12 +6999,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>recuperacao_percentual</t>
+          <t>acm_faixa_aceitacao_operador</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -7114,24 +7015,24 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>50</v>
+        <v>132</v>
       </c>
       <c r="B51" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>results_extract</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>acm_faixa_aceitacao_minimo</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -7142,24 +7043,24 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>51</v>
+        <v>133</v>
       </c>
       <c r="B52" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>results_extract</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>acm_faixa_aceitacao_maximo</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -7170,19 +7071,19 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>52</v>
+        <v>134</v>
       </c>
       <c r="B53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>results_extract</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>acm_faixa_aceitacao_unidade</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -7198,24 +7099,24 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="B54" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>results_extract</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>variacao_percentual</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -7226,24 +7127,24 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="B55" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>results_extract</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>quantidade_adicionada</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7254,24 +7155,24 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>55</v>
+        <v>137</v>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>results_extract</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>proposta_comercial</t>
+          <t>recuperacao_percentual</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7282,19 +7183,19 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>56</v>
+        <v>138</v>
       </c>
       <c r="B57" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>cliente</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -7310,24 +7211,24 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>57</v>
+        <v>139</v>
       </c>
       <c r="B58" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>cnpj_cpf</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -7338,19 +7239,19 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>58</v>
+        <v>140</v>
       </c>
       <c r="B59" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>contato</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7366,24 +7267,24 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>59</v>
+        <v>141</v>
       </c>
       <c r="B60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>telefone</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -7394,24 +7295,24 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>60</v>
+        <v>142</v>
       </c>
       <c r="B61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>endereco</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7422,24 +7323,24 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>61</v>
+        <v>143</v>
       </c>
       <c r="B62" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7450,24 +7351,24 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>62</v>
+        <v>144</v>
       </c>
       <c r="B63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7478,19 +7379,19 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>63</v>
+        <v>145</v>
       </c>
       <c r="B64" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>tipo_amostra</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -7506,24 +7407,24 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>64</v>
+        <v>146</v>
       </c>
       <c r="B65" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>criterio_conformidade</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7534,24 +7435,24 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>65</v>
+        <v>147</v>
       </c>
       <c r="B66" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>data_coleta</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7562,24 +7463,24 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>66</v>
+        <v>148</v>
       </c>
       <c r="B67" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>tabela_indice</t>
+          <t>data_publicacao</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7590,24 +7491,24 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>67</v>
+        <v>149</v>
       </c>
       <c r="B68" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>categoria</t>
+          <t>data_recebimento</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7618,19 +7519,19 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="B69" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>subcategoria</t>
+          <t>observacoes</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7646,24 +7547,24 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>69</v>
+        <v>151</v>
       </c>
       <c r="B70" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>tipo_registro</t>
+          <t>dh_inicio_atividade</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_ou_data_hora</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7674,19 +7575,19 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="B71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>modo_auditoria</t>
+          <t>localizacao</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7702,24 +7603,24 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>71</v>
+        <v>153</v>
       </c>
       <c r="B72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>cabecalho_detectado</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7730,24 +7631,24 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="B73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>colunas_detectadas</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7758,19 +7659,19 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>73</v>
+        <v>155</v>
       </c>
       <c r="B74" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>colunas_mapeadas</t>
+          <t>clima_ultimas_24h</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -7786,19 +7687,19 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="B75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>colunas_sem_mapeamento</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7814,19 +7715,19 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>75</v>
+        <v>157</v>
       </c>
       <c r="B76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>campos_esperados</t>
+          <t>tipo_coleta</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7842,19 +7743,19 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>76</v>
+        <v>158</v>
       </c>
       <c r="B77" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>campos_obrigatorios_ausentes</t>
+          <t>responsavel_amostra</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7870,19 +7771,19 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="B78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>campos_opcionais_ausentes</t>
+          <t>planejamento_amostragem</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7898,19 +7799,19 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>78</v>
+        <v>160</v>
       </c>
       <c r="B79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>usou_fallback</t>
+          <t>descricao_nao_conformidade</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7926,19 +7827,19 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>79</v>
+        <v>161</v>
       </c>
       <c r="B80" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>codigo_laudo_substituido</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7954,19 +7855,19 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="B81" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>observacao</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7982,24 +7883,24 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="B82" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>classification_audit_estrutura</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>estrutura_auditoria</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -8010,24 +7911,24 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>82</v>
+        <v>164</v>
       </c>
       <c r="B83" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>validation_errors_estrutura</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>estrutura_auditoria</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -8038,19 +7939,19 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>83</v>
+        <v>165</v>
       </c>
       <c r="B84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -8066,24 +7967,24 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>84</v>
+        <v>166</v>
       </c>
       <c r="B85" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8094,24 +7995,24 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>85</v>
+        <v>167</v>
       </c>
       <c r="B86" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -8122,24 +8023,24 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>86</v>
+        <v>168</v>
       </c>
       <c r="B87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>proposta_comercial</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -8150,19 +8051,19 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>87</v>
+        <v>169</v>
       </c>
       <c r="B88" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>metadata</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>subtipo_amostra</t>
+          <t>cliente</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -8178,19 +8079,19 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>88</v>
+        <v>170</v>
       </c>
       <c r="B89" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>cnpj_cpf</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8206,24 +8107,24 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>89</v>
+        <v>171</v>
       </c>
       <c r="B90" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>contato</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -8234,19 +8135,19 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>90</v>
+        <v>172</v>
       </c>
       <c r="B91" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>telefone</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8262,24 +8163,24 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>91</v>
+        <v>173</v>
       </c>
       <c r="B92" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>endereco</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -8290,24 +8191,24 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>92</v>
+        <v>174</v>
       </c>
       <c r="B93" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -8318,24 +8219,24 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>93</v>
+        <v>175</v>
       </c>
       <c r="B94" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -8346,19 +8247,19 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>94</v>
+        <v>176</v>
       </c>
       <c r="B95" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>embalagem</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8374,24 +8275,24 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>95</v>
+        <v>177</v>
       </c>
       <c r="B96" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -8402,24 +8303,24 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>96</v>
+        <v>178</v>
       </c>
       <c r="B97" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>preservacao</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -8430,24 +8331,24 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>97</v>
+        <v>179</v>
       </c>
       <c r="B98" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -8458,24 +8359,24 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>98</v>
+        <v>180</v>
       </c>
       <c r="B99" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>tabela_indice</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -8486,24 +8387,24 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>99</v>
+        <v>181</v>
       </c>
       <c r="B100" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>categoria</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8514,19 +8415,19 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>100</v>
+        <v>182</v>
       </c>
       <c r="B101" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>subcategoria</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8542,24 +8443,24 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>101</v>
+        <v>183</v>
       </c>
       <c r="B102" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>tipo_registro</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8570,24 +8471,24 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>102</v>
+        <v>184</v>
       </c>
       <c r="B103" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>modo_auditoria</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8598,24 +8499,24 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>103</v>
+        <v>185</v>
       </c>
       <c r="B104" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>cabecalho_detectado</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8626,19 +8527,19 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>104</v>
+        <v>186</v>
       </c>
       <c r="B105" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>colunas_detectadas</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8654,19 +8555,19 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>105</v>
+        <v>187</v>
       </c>
       <c r="B106" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>colunas_mapeadas</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8682,24 +8583,24 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>106</v>
+        <v>188</v>
       </c>
       <c r="B107" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>colunas_sem_mapeamento</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8710,19 +8611,19 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>107</v>
+        <v>189</v>
       </c>
       <c r="B108" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>campos_esperados</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8738,24 +8639,24 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>108</v>
+        <v>190</v>
       </c>
       <c r="B109" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>campos_obrigatorios_ausentes</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8766,24 +8667,24 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>109</v>
+        <v>191</v>
       </c>
       <c r="B110" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>campos_opcionais_ausentes</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -8794,24 +8695,24 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>110</v>
+        <v>192</v>
       </c>
       <c r="B111" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>usou_fallback</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8822,19 +8723,19 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>111</v>
+        <v>193</v>
       </c>
       <c r="B112" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8850,19 +8751,19 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>112</v>
+        <v>194</v>
       </c>
       <c r="B113" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>observacao</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8878,24 +8779,24 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>113</v>
+        <v>195</v>
       </c>
       <c r="B114" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -8906,24 +8807,24 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>114</v>
+        <v>196</v>
       </c>
       <c r="B115" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -8934,24 +8835,24 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>115</v>
+        <v>197</v>
       </c>
       <c r="B116" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -8962,19 +8863,19 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>116</v>
+        <v>198</v>
       </c>
       <c r="B117" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8990,24 +8891,24 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>117</v>
+        <v>199</v>
       </c>
       <c r="B118" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -9018,19 +8919,19 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>118</v>
+        <v>200</v>
       </c>
       <c r="B119" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>template_avaliado</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -9046,24 +8947,24 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119</v>
+        <v>201</v>
       </c>
       <c r="B120" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>score</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -9074,24 +8975,24 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>120</v>
+        <v>202</v>
       </c>
       <c r="B121" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>score_minimo</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -9102,24 +9003,24 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>121</v>
+        <v>203</v>
       </c>
       <c r="B122" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>prioridade</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -9130,24 +9031,24 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122</v>
+        <v>204</v>
       </c>
       <c r="B123" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -9158,24 +9059,24 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>123</v>
+        <v>205</v>
       </c>
       <c r="B124" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>regras_encontradas</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -9186,24 +9087,24 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124</v>
+        <v>206</v>
       </c>
       <c r="B125" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -9214,19 +9115,19 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>125</v>
+        <v>207</v>
       </c>
       <c r="B126" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>chave_validacao</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -9242,24 +9143,24 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>126</v>
+        <v>208</v>
       </c>
       <c r="B127" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>row_number</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -9270,24 +9171,24 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>127</v>
+        <v>209</v>
       </c>
       <c r="B128" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>caminho_arquivo</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -9298,24 +9199,24 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128</v>
+        <v>210</v>
       </c>
       <c r="B129" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -9326,19 +9227,19 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>129</v>
+        <v>211</v>
       </c>
       <c r="B130" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>field</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -9354,24 +9255,24 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>130</v>
+        <v>212</v>
       </c>
       <c r="B131" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>error_type</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -9382,24 +9283,24 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>131</v>
+        <v>213</v>
       </c>
       <c r="B132" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>message</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -9410,19 +9311,19 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>132</v>
+        <v>214</v>
       </c>
       <c r="B133" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -9438,19 +9339,19 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133</v>
+        <v>215</v>
       </c>
       <c r="B134" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>data_publicacao</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -9466,24 +9367,24 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>134</v>
+        <v>216</v>
       </c>
       <c r="B135" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -9494,19 +9395,19 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>135</v>
+        <v>217</v>
       </c>
       <c r="B136" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>hash_arquivo</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9522,24 +9423,24 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>136</v>
+        <v>218</v>
       </c>
       <c r="B137" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>hash_texto</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -9550,24 +9451,24 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>137</v>
+        <v>219</v>
       </c>
       <c r="B138" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>grupo_duplicidade</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -9578,24 +9479,24 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>138</v>
+        <v>220</v>
       </c>
       <c r="B139" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>tipo_duplicidade</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -9606,19 +9507,19 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>139</v>
+        <v>221</v>
       </c>
       <c r="B140" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>arquivo_referencia</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -9634,19 +9535,19 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>140</v>
+        <v>222</v>
       </c>
       <c r="B141" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>motivo</t>
+          <t>embalagem</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9662,19 +9563,19 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>141</v>
+        <v>223</v>
       </c>
       <c r="B142" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9690,19 +9591,19 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>142</v>
+        <v>224</v>
       </c>
       <c r="B143" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>preservacao</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9718,24 +9619,24 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>143</v>
+        <v>225</v>
       </c>
       <c r="B144" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -9746,19 +9647,19 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>144</v>
+        <v>226</v>
       </c>
       <c r="B145" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9774,19 +9675,19 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>145</v>
+        <v>227</v>
       </c>
       <c r="B146" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9802,24 +9703,24 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>146</v>
+        <v>228</v>
       </c>
       <c r="B147" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -9830,24 +9731,24 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>147</v>
+        <v>229</v>
       </c>
       <c r="B148" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9858,24 +9759,24 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>148</v>
+        <v>230</v>
       </c>
       <c r="B149" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>tipo_amostra</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9886,24 +9787,24 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>149</v>
+        <v>231</v>
       </c>
       <c r="B150" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>criterio_conformidade</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9914,24 +9815,24 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>150</v>
+        <v>232</v>
       </c>
       <c r="B151" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9942,24 +9843,24 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>151</v>
+        <v>233</v>
       </c>
       <c r="B152" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>dh_coleta</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -9970,24 +9871,24 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>152</v>
+        <v>234</v>
       </c>
       <c r="B153" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>data_publicacao</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -9998,24 +9899,24 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>153</v>
+        <v>235</v>
       </c>
       <c r="B154" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>dh_publicacao</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -10026,24 +9927,24 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>154</v>
+        <v>236</v>
       </c>
       <c r="B155" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>data_recebimento</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -10054,24 +9955,24 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>155</v>
+        <v>237</v>
       </c>
       <c r="B156" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>dh_recebimento</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -10082,24 +9983,24 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>156</v>
+        <v>238</v>
       </c>
       <c r="B157" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>observacoes</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -10110,24 +10011,24 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>157</v>
+        <v>239</v>
       </c>
       <c r="B158" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>dh_inicio_atividade</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>data_ou_data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -10138,24 +10039,24 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>158</v>
+        <v>240</v>
       </c>
       <c r="B159" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>localizacao</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -10166,24 +10067,24 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>159</v>
+        <v>241</v>
       </c>
       <c r="B160" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -10194,24 +10095,24 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>160</v>
+        <v>242</v>
       </c>
       <c r="B161" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -10222,24 +10123,24 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>162</v>
+        <v>243</v>
       </c>
       <c r="B162" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>clima_ultimas_24h</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -10250,19 +10151,19 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>163</v>
+        <v>244</v>
       </c>
       <c r="B163" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10278,24 +10179,24 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>164</v>
+        <v>245</v>
       </c>
       <c r="B164" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>tipo_coleta</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -10306,24 +10207,24 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>165</v>
+        <v>246</v>
       </c>
       <c r="B165" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>responsavel_amostra</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -10334,24 +10235,24 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>166</v>
+        <v>247</v>
       </c>
       <c r="B166" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>planejamento_amostragem</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -10362,24 +10263,24 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>167</v>
+        <v>248</v>
       </c>
       <c r="B167" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>descricao_nao_conformidade</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -10390,19 +10291,19 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>168</v>
+        <v>249</v>
       </c>
       <c r="B168" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>codigo_laudo_substituido</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -10411,6 +10312,706 @@
         </is>
       </c>
       <c r="F168" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>250</v>
+      </c>
+      <c r="B169" t="n">
+        <v>12</v>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>251</v>
+      </c>
+      <c r="B170" t="n">
+        <v>12</v>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>252</v>
+      </c>
+      <c r="B171" t="n">
+        <v>12</v>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>253</v>
+      </c>
+      <c r="B172" t="n">
+        <v>12</v>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>versao_template</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>254</v>
+      </c>
+      <c r="B173" t="n">
+        <v>12</v>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>acm_data_hora_extracao</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>data_hora</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>255</v>
+      </c>
+      <c r="B174" t="n">
+        <v>12</v>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>id_amostra</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>256</v>
+      </c>
+      <c r="B175" t="n">
+        <v>12</v>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>pagina</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>257</v>
+      </c>
+      <c r="B176" t="n">
+        <v>12</v>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>chave_validacao</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>258</v>
+      </c>
+      <c r="B177" t="n">
+        <v>20</v>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>259</v>
+      </c>
+      <c r="B178" t="n">
+        <v>20</v>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>caminho_arquivo</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>260</v>
+      </c>
+      <c r="B179" t="n">
+        <v>20</v>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>261</v>
+      </c>
+      <c r="B180" t="n">
+        <v>20</v>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>262</v>
+      </c>
+      <c r="B181" t="n">
+        <v>20</v>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>versao_template</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>263</v>
+      </c>
+      <c r="B182" t="n">
+        <v>20</v>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>acm_data_hora_extracao</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>data_hora</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="n">
+        <v>264</v>
+      </c>
+      <c r="B183" t="n">
+        <v>20</v>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>id_amostra</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="n">
+        <v>265</v>
+      </c>
+      <c r="B184" t="n">
+        <v>20</v>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>identificacao_amostra</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="n">
+        <v>266</v>
+      </c>
+      <c r="B185" t="n">
+        <v>20</v>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>data_publicacao</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>data_hora</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="n">
+        <v>267</v>
+      </c>
+      <c r="B186" t="n">
+        <v>20</v>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>data_coleta</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>data_hora</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="n">
+        <v>268</v>
+      </c>
+      <c r="B187" t="n">
+        <v>20</v>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>hash_arquivo</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="n">
+        <v>269</v>
+      </c>
+      <c r="B188" t="n">
+        <v>20</v>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>hash_texto</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="n">
+        <v>270</v>
+      </c>
+      <c r="B189" t="n">
+        <v>20</v>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>grupo_duplicidade</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="n">
+        <v>271</v>
+      </c>
+      <c r="B190" t="n">
+        <v>20</v>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>tipo_duplicidade</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="n">
+        <v>272</v>
+      </c>
+      <c r="B191" t="n">
+        <v>20</v>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>arquivo_referencia</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="n">
+        <v>273</v>
+      </c>
+      <c r="B192" t="n">
+        <v>20</v>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>motivo</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="n">
+        <v>274</v>
+      </c>
+      <c r="B193" t="n">
+        <v>20</v>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
         <is>
           <t>sim</t>
         </is>

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -5598,7 +5598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9.7265625" customWidth="1" min="1" max="1"/>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>codigo_laudo_substituido</t>
+          <t>acm_codigo_laudo</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>codigo_laudo_substituido</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>resultado</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6159,12 +6159,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>acm_resultado_tratado</t>
+          <t>resultado</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -6187,7 +6187,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>acm_qualificador</t>
+          <t>unidade</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -6215,12 +6215,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>acm_unidade</t>
+          <t>acm_resultado_tratado</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -6243,7 +6243,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>local</t>
+          <t>acm_qualificador</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>data_inicio</t>
+          <t>acm_unidade</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>data</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>conama</t>
+          <t>local</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>acm_conama_operador</t>
+          <t>data_inicio</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -6355,12 +6355,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>acm_conama_minimo</t>
+          <t>conama</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6383,12 +6383,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>acm_conama_maximo</t>
+          <t>acm_conama_operador</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>acm_conama_unidade</t>
+          <t>acm_conama_minimo</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -6439,12 +6439,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>copam_cerh</t>
+          <t>acm_conama_maximo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_operador</t>
+          <t>acm_conama_unidade</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_minimo</t>
+          <t>copam_cerh</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_maximo</t>
+          <t>acm_copam_cerh_operador</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_unidade</t>
+          <t>acm_copam_cerh_minimo</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>ld</t>
+          <t>acm_copam_cerh_maximo</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6607,12 +6607,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>acm_ld_minimo</t>
+          <t>acm_copam_cerh_unidade</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6635,12 +6635,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>acm_ld_maximo</t>
+          <t>ld</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>acm_ld_unidade</t>
+          <t>acm_ld_minimo</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -6691,12 +6691,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>lq</t>
+          <t>acm_ld_maximo</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>acm_lq_minimo</t>
+          <t>acm_ld_unidade</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -6747,12 +6747,12 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>acm_lq_maximo</t>
+          <t>lq</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>acm_lq_unidade</t>
+          <t>acm_lq_minimo</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>referencia</t>
+          <t>acm_lq_maximo</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>incerteza</t>
+          <t>acm_lq_unidade</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -6859,12 +6859,12 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>acm_incerteza_valor</t>
+          <t>referencia</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>acm_incerteza_unidade</t>
+          <t>incerteza</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>numero_cq</t>
+          <t>acm_incerteza_valor</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>duplicata</t>
+          <t>acm_incerteza_unidade</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>texto_numerico</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>faixa_aceitacao</t>
+          <t>numero_cq</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6999,12 +6999,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_operador</t>
+          <t>duplicata</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>texto_numerico</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_minimo</t>
+          <t>faixa_aceitacao</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -7055,12 +7055,12 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_maximo</t>
+          <t>acm_faixa_aceitacao_operador</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_unidade</t>
+          <t>acm_faixa_aceitacao_minimo</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>variacao_percentual</t>
+          <t>acm_faixa_aceitacao_maximo</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>quantidade_adicionada</t>
+          <t>acm_faixa_aceitacao_unidade</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7167,7 +7167,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>recuperacao_percentual</t>
+          <t>variacao_percentual</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -7186,21 +7186,21 @@
         <v>138</v>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>results_extract</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>quantidade_adicionada</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -7214,21 +7214,21 @@
         <v>139</v>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>results_extract</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>recuperacao_percentual</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -7251,7 +7251,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>tipo_amostra</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>criterio_conformidade</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>tipo_amostra</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -7475,12 +7475,12 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>data_publicacao</t>
+          <t>criterio_conformidade</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>data_recebimento</t>
+          <t>data_coleta</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>observacoes</t>
+          <t>data_publicacao</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>dh_inicio_atividade</t>
+          <t>data_recebimento</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>data_ou_data_hora</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7587,7 +7587,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>localizacao</t>
+          <t>observacoes</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>dh_inicio_atividade</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>data_ou_data_hora</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>localizacao</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>clima_ultimas_24h</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7699,12 +7699,12 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>tipo_coleta</t>
+          <t>clima_ultimas_24h</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>responsavel_amostra</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>planejamento_amostragem</t>
+          <t>tipo_coleta</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>descricao_nao_conformidade</t>
+          <t>responsavel_amostra</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>codigo_laudo_substituido</t>
+          <t>planejamento_amostragem</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7858,16 +7858,16 @@
         <v>162</v>
       </c>
       <c r="B81" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>descricao_nao_conformidade</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7886,21 +7886,21 @@
         <v>163</v>
       </c>
       <c r="B82" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>codigo_laudo_substituido</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7923,7 +7923,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8007,7 +8007,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>proposta_comercial</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>cliente</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -8091,7 +8091,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>cnpj_cpf</t>
+          <t>proposta_comercial</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>contato</t>
+          <t>cliente</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>telefone</t>
+          <t>cnpj_cpf</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>endereco</t>
+          <t>contato</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8194,16 +8194,16 @@
         <v>174</v>
       </c>
       <c r="B93" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>telefone</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8222,21 +8222,21 @@
         <v>175</v>
       </c>
       <c r="B94" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>endereco</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8287,7 +8287,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -8343,7 +8343,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>tabela_indice</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>categoria</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8427,12 +8427,12 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>subcategoria</t>
+          <t>tabela_indice</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>tipo_registro</t>
+          <t>categoria</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>modo_auditoria</t>
+          <t>subcategoria</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>cabecalho_detectado</t>
+          <t>tipo_registro</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>colunas_detectadas</t>
+          <t>modo_auditoria</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>colunas_mapeadas</t>
+          <t>cabecalho_detectado</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>colunas_sem_mapeamento</t>
+          <t>colunas_detectadas</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>campos_esperados</t>
+          <t>colunas_mapeadas</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>campos_obrigatorios_ausentes</t>
+          <t>colunas_sem_mapeamento</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>campos_opcionais_ausentes</t>
+          <t>campos_esperados</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>usou_fallback</t>
+          <t>campos_obrigatorios_ausentes</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>campos_opcionais_ausentes</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>observacao</t>
+          <t>usou_fallback</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8782,16 +8782,16 @@
         <v>195</v>
       </c>
       <c r="B114" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8810,21 +8810,21 @@
         <v>196</v>
       </c>
       <c r="B115" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>observacao</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8875,7 +8875,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>template_avaliado</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>score_minimo</t>
+          <t>template_avaliado</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -9015,12 +9015,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>prioridade</t>
+          <t>score</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -9043,12 +9043,12 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>score_minimo</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>regras_encontradas</t>
+          <t>prioridade</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -9090,21 +9090,21 @@
         <v>206</v>
       </c>
       <c r="B125" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>207</v>
       </c>
       <c r="B126" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>regras_encontradas</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -9155,12 +9155,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>row_number</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -9211,12 +9211,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>row_number</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>field</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>error_type</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>field</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>error_type</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -9342,16 +9342,16 @@
         <v>215</v>
       </c>
       <c r="B134" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>message</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -9370,21 +9370,21 @@
         <v>216</v>
       </c>
       <c r="B135" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -9407,7 +9407,7 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9435,7 +9435,7 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -9491,7 +9491,7 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -9547,12 +9547,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>embalagem</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -9575,7 +9575,7 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>preservacao</t>
+          <t>embalagem</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9650,16 +9650,16 @@
         <v>226</v>
       </c>
       <c r="B145" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>preservacao</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9678,21 +9678,21 @@
         <v>227</v>
       </c>
       <c r="B146" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -9715,7 +9715,7 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9855,12 +9855,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -9874,21 +9874,21 @@
         <v>234</v>
       </c>
       <c r="B153" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -9902,21 +9902,21 @@
         <v>235</v>
       </c>
       <c r="B154" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -10023,7 +10023,7 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -10079,12 +10079,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -10098,21 +10098,21 @@
         <v>242</v>
       </c>
       <c r="B161" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -10126,21 +10126,21 @@
         <v>243</v>
       </c>
       <c r="B162" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -10247,7 +10247,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -10322,21 +10322,21 @@
         <v>250</v>
       </c>
       <c r="B169" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -10350,21 +10350,21 @@
         <v>251</v>
       </c>
       <c r="B170" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -10387,7 +10387,7 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -10443,12 +10443,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -10471,7 +10471,7 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10499,12 +10499,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -10527,12 +10527,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>chave_validacao</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -10546,21 +10546,21 @@
         <v>258</v>
       </c>
       <c r="B177" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -10574,16 +10574,16 @@
         <v>259</v>
       </c>
       <c r="B178" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>caminho_arquivo</t>
+          <t>chave_validacao</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -10611,12 +10611,12 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>caminho_arquivo</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10667,7 +10667,7 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -10723,7 +10723,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>data_publicacao</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10807,12 +10807,12 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10835,12 +10835,12 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>hash_arquivo</t>
+          <t>data_publicacao</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -10863,12 +10863,12 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>hash_texto</t>
+          <t>data_coleta</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>grupo_duplicidade</t>
+          <t>hash_arquivo</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>tipo_duplicidade</t>
+          <t>hash_texto</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>arquivo_referencia</t>
+          <t>grupo_duplicidade</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>motivo</t>
+          <t>tipo_duplicidade</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11003,15 +11003,71 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
+          <t>arquivo_referencia</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="n">
+        <v>275</v>
+      </c>
+      <c r="B194" t="n">
+        <v>20</v>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>motivo</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="n">
+        <v>276</v>
+      </c>
+      <c r="B195" t="n">
+        <v>20</v>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="E193" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="F193" t="inlineStr">
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
         <is>
           <t>sim</t>
         </is>

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -5598,7 +5598,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F195"/>
+  <dimension ref="A1:F196"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9.7265625" customWidth="1" min="1" max="1"/>
@@ -6355,12 +6355,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>conama</t>
+          <t>acm_data_inicio</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -6383,7 +6383,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>acm_conama_operador</t>
+          <t>conama</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>acm_conama_minimo</t>
+          <t>acm_conama_operador</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>acm_conama_maximo</t>
+          <t>acm_conama_minimo</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6467,12 +6467,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>acm_conama_unidade</t>
+          <t>acm_conama_maximo</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6495,7 +6495,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>copam_cerh</t>
+          <t>acm_conama_unidade</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_operador</t>
+          <t>copam_cerh</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_minimo</t>
+          <t>acm_copam_cerh_operador</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6579,7 +6579,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_maximo</t>
+          <t>acm_copam_cerh_minimo</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -6607,12 +6607,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>acm_copam_cerh_unidade</t>
+          <t>acm_copam_cerh_maximo</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6635,7 +6635,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>ld</t>
+          <t>acm_copam_cerh_unidade</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -6663,12 +6663,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>acm_ld_minimo</t>
+          <t>ld</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>acm_ld_maximo</t>
+          <t>acm_ld_minimo</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>acm_ld_unidade</t>
+          <t>acm_ld_maximo</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>lq</t>
+          <t>acm_ld_unidade</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>acm_lq_minimo</t>
+          <t>lq</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>acm_lq_maximo</t>
+          <t>acm_lq_minimo</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>acm_lq_unidade</t>
+          <t>acm_lq_maximo</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -6859,7 +6859,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>referencia</t>
+          <t>acm_lq_unidade</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -6887,7 +6887,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>incerteza</t>
+          <t>referencia</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>acm_incerteza_valor</t>
+          <t>incerteza</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>acm_incerteza_unidade</t>
+          <t>acm_incerteza_valor</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>numero_cq</t>
+          <t>acm_incerteza_unidade</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -6999,12 +6999,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>duplicata</t>
+          <t>numero_cq</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>texto_numerico</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -7027,12 +7027,12 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>faixa_aceitacao</t>
+          <t>duplicata</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>texto_numerico</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_operador</t>
+          <t>faixa_aceitacao</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_minimo</t>
+          <t>acm_faixa_aceitacao_operador</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -7111,7 +7111,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_maximo</t>
+          <t>acm_faixa_aceitacao_minimo</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>acm_faixa_aceitacao_unidade</t>
+          <t>acm_faixa_aceitacao_maximo</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -7167,12 +7167,12 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>variacao_percentual</t>
+          <t>acm_faixa_aceitacao_unidade</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -7195,7 +7195,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>quantidade_adicionada</t>
+          <t>variacao_percentual</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>recuperacao_percentual</t>
+          <t>quantidade_adicionada</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -7242,21 +7242,21 @@
         <v>140</v>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>results_extract</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>recuperacao_percentual</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -7279,12 +7279,12 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -7335,12 +7335,12 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -7419,12 +7419,12 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -7447,7 +7447,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>tipo_amostra</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7475,7 +7475,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>criterio_conformidade</t>
+          <t>tipo_amostra</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>criterio_conformidade</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>data_publicacao</t>
+          <t>data_coleta</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>data_recebimento</t>
+          <t>data_publicacao</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -7587,12 +7587,12 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>observacoes</t>
+          <t>data_recebimento</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>dh_inicio_atividade</t>
+          <t>observacoes</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>data_ou_data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>localizacao</t>
+          <t>dh_inicio_atividade</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_ou_data_hora</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7671,12 +7671,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>localizacao</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7699,7 +7699,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>clima_ultimas_24h</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7755,7 +7755,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>clima_ultimas_24h</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>tipo_coleta</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7811,7 +7811,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>responsavel_amostra</t>
+          <t>tipo_coleta</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7839,7 +7839,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>planejamento_amostragem</t>
+          <t>responsavel_amostra</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>descricao_nao_conformidade</t>
+          <t>planejamento_amostragem</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -7895,7 +7895,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>codigo_laudo_substituido</t>
+          <t>descricao_nao_conformidade</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -7914,16 +7914,16 @@
         <v>164</v>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>codigo_laudo_substituido</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -7951,12 +7951,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8007,12 +8007,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -8035,12 +8035,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -8063,12 +8063,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -8091,12 +8091,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>proposta_comercial</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>cliente</t>
+          <t>proposta_comercial</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8147,7 +8147,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>cnpj_cpf</t>
+          <t>cliente</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8175,7 +8175,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>contato</t>
+          <t>cnpj_cpf</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8203,7 +8203,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>telefone</t>
+          <t>contato</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8231,7 +8231,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>endereco</t>
+          <t>telefone</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8250,16 +8250,16 @@
         <v>176</v>
       </c>
       <c r="B95" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>endereco</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8287,12 +8287,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -8315,12 +8315,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -8343,12 +8343,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -8371,12 +8371,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>tabela_indice</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>categoria</t>
+          <t>tabela_indice</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>subcategoria</t>
+          <t>categoria</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>tipo_registro</t>
+          <t>subcategoria</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>modo_auditoria</t>
+          <t>tipo_registro</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>cabecalho_detectado</t>
+          <t>modo_auditoria</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8595,7 +8595,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>colunas_detectadas</t>
+          <t>cabecalho_detectado</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -8623,7 +8623,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>colunas_mapeadas</t>
+          <t>colunas_detectadas</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>colunas_sem_mapeamento</t>
+          <t>colunas_mapeadas</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8679,7 +8679,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>campos_esperados</t>
+          <t>colunas_sem_mapeamento</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>campos_obrigatorios_ausentes</t>
+          <t>campos_esperados</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8735,7 +8735,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>campos_opcionais_ausentes</t>
+          <t>campos_obrigatorios_ausentes</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8763,7 +8763,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>usou_fallback</t>
+          <t>campos_opcionais_ausentes</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8791,7 +8791,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>usou_fallback</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>observacao</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8838,16 +8838,16 @@
         <v>197</v>
       </c>
       <c r="B116" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>observacao</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -8875,12 +8875,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -8903,12 +8903,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -8987,12 +8987,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>template_avaliado</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -9015,12 +9015,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>template_avaliado</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>score_minimo</t>
+          <t>score</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>prioridade</t>
+          <t>score_minimo</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -9099,12 +9099,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>prioridade</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>regras_encontradas</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -9146,21 +9146,21 @@
         <v>208</v>
       </c>
       <c r="B127" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>regras_encontradas</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -9211,12 +9211,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>row_number</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>row_number</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -9267,12 +9267,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -9295,7 +9295,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>field</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -9323,7 +9323,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>error_type</t>
+          <t>field</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>error_type</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -9379,7 +9379,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>message</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -9398,16 +9398,16 @@
         <v>217</v>
       </c>
       <c r="B136" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9435,12 +9435,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -9463,12 +9463,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -9491,12 +9491,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -9547,12 +9547,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -9575,12 +9575,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -9603,7 +9603,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>embalagem</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>embalagem</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9659,7 +9659,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>preservacao</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>preservacao</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9706,16 +9706,16 @@
         <v>228</v>
       </c>
       <c r="B147" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9743,12 +9743,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9771,12 +9771,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9799,12 +9799,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9855,12 +9855,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -9911,12 +9911,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -9930,16 +9930,16 @@
         <v>236</v>
       </c>
       <c r="B155" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -9995,12 +9995,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -10023,12 +10023,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -10051,12 +10051,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -10079,12 +10079,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -10107,7 +10107,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10135,12 +10135,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -10154,16 +10154,16 @@
         <v>244</v>
       </c>
       <c r="B163" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -10247,12 +10247,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -10378,16 +10378,16 @@
         <v>252</v>
       </c>
       <c r="B171" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10415,12 +10415,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -10443,12 +10443,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -10499,12 +10499,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -10527,12 +10527,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -10555,7 +10555,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>chave_validacao</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -10602,16 +10602,16 @@
         <v>260</v>
       </c>
       <c r="B179" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>chave_validacao</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10639,7 +10639,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>caminho_arquivo</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10667,12 +10667,12 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>caminho_arquivo</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -10695,12 +10695,12 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -10723,12 +10723,12 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -10751,12 +10751,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10807,12 +10807,12 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10835,12 +10835,12 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>data_publicacao</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -10863,7 +10863,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>data_publicacao</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -10891,12 +10891,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>hash_arquivo</t>
+          <t>data_coleta</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -10919,7 +10919,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>hash_texto</t>
+          <t>hash_arquivo</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -10947,7 +10947,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>grupo_duplicidade</t>
+          <t>hash_texto</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -10975,7 +10975,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>tipo_duplicidade</t>
+          <t>grupo_duplicidade</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>arquivo_referencia</t>
+          <t>tipo_duplicidade</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11031,7 +11031,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>motivo</t>
+          <t>arquivo_referencia</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11059,15 +11059,43 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
+          <t>motivo</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="n">
+        <v>277</v>
+      </c>
+      <c r="B196" t="n">
+        <v>20</v>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>duplicate_audit</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
           <t>status</t>
         </is>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="F195" t="inlineStr">
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
         <is>
           <t>sim</t>
         </is>

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G140"/>
+  <dimension ref="A1:G144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>(?:^|\n)\s*Notas?\s*:?\s*(.*?)(?=\n\s*(?:Considera..es\s+Gerais|Declara..o\s+de\s+Conformidade|Chave\s+de\s+Valida..o|$))</t>
+          <t>(?:^|\n)[ \t]*Notas?[ \t]*:?[ \t]*(?:\n|$)(.*?)(?=\n[ \t]*(?:Considera..es\s+Gerais|Declara..o\s+de\s+Conformidade|Chave\s+de\s+Valida..o|Embalagens\s+e\s+Preservantes|Registro\s+da\s+Coleta|FO-ANL-\d+|Revis.o\s*:|Pag\.\s*\d+|CEP\s*:|Aprova..o\s*:)|\Z)</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>descricao=Extrai o bloco textual de Notas.</t>
+          <t>descricao=Extrai integralmente o bloco de Notas ate a proxima secao ou rodape.</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -5178,6 +5178,138 @@
         </is>
       </c>
       <c r="G140" t="inlineStr">
+        <is>
+          <t>N?o se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>143</v>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>section_start</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>(?:^|\n)\s*Notas?\s*:?</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>descricao=Identifica o inicio da secao de Notas.</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>N?o se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>144</v>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>general_considerations</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>section_start</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>(?:^|\n)\s*Considera..es\s+Gerais\s*:?</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>descricao=Identifica o inicio da secao de Consideracoes Gerais.</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>N?o se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>145</v>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>conformity_statement</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>section_start</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>(?:^|\n)\s*Declara..o\s+de\s+Conformidade\s*:?</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>descricao=Identifica o inicio da secao de Declaracao de Conformidade.</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>N?o se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>146</v>
+      </c>
+      <c r="B144" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>section_start</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>(?:^|\n)\s*Chave\s+de\s+Valida..o\s*:?</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>descricao=Identifica o inicio da secao de Chave de Validacao.</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
         <is>
           <t>N?o se aplica</t>
         </is>
@@ -5195,7 +5327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="13.54296875" customWidth="1" min="1" max="1"/>
@@ -5581,6 +5713,24 @@
         </is>
       </c>
       <c r="D21" t="inlineStr">
+        <is>
+          <t>Verdadeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Verdadeiro</t>
         </is>
@@ -5598,7 +5748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F196"/>
+  <dimension ref="A1:F212"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9.7265625" customWidth="1" min="1" max="1"/>
@@ -11101,6 +11251,454 @@
         </is>
       </c>
     </row>
+    <row r="197">
+      <c r="A197" t="n">
+        <v>278</v>
+      </c>
+      <c r="B197" t="n">
+        <v>21</v>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="n">
+        <v>279</v>
+      </c>
+      <c r="B198" t="n">
+        <v>21</v>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="n">
+        <v>280</v>
+      </c>
+      <c r="B199" t="n">
+        <v>21</v>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="n">
+        <v>281</v>
+      </c>
+      <c r="B200" t="n">
+        <v>21</v>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>versao_template</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="n">
+        <v>282</v>
+      </c>
+      <c r="B201" t="n">
+        <v>21</v>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>acm_data_hora_extracao</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>data_hora</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="n">
+        <v>283</v>
+      </c>
+      <c r="B202" t="n">
+        <v>21</v>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>pagina</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="n">
+        <v>284</v>
+      </c>
+      <c r="B203" t="n">
+        <v>21</v>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>tabela_indice</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="n">
+        <v>285</v>
+      </c>
+      <c r="B204" t="n">
+        <v>21</v>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>objeto_tipo</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="n">
+        <v>286</v>
+      </c>
+      <c r="B205" t="n">
+        <v>21</v>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>secao</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="n">
+        <v>287</v>
+      </c>
+      <c r="B206" t="n">
+        <v>21</v>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>titulo_detectado</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="n">
+        <v>288</v>
+      </c>
+      <c r="B207" t="n">
+        <v>21</v>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>modo_auditoria</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="n">
+        <v>289</v>
+      </c>
+      <c r="B208" t="n">
+        <v>21</v>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>regra_encontrada</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="n">
+        <v>290</v>
+      </c>
+      <c r="B209" t="n">
+        <v>21</v>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>ocorrencias_detectadas</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="n">
+        <v>291</v>
+      </c>
+      <c r="B210" t="n">
+        <v>21</v>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>registros_extraidos</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="n">
+        <v>292</v>
+      </c>
+      <c r="B211" t="n">
+        <v>21</v>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>293</v>
+      </c>
+      <c r="B212" t="n">
+        <v>21</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>section_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>observacao</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -5748,7 +5748,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F212"/>
+  <dimension ref="A1:F211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9.7265625" customWidth="1" min="1" max="1"/>
@@ -7781,7 +7781,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B73" t="n">
         <v>3</v>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>dh_inicio_atividade</t>
+          <t>localizacao</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>data_ou_data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7809,7 +7809,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B74" t="n">
         <v>3</v>
@@ -7821,12 +7821,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>localizacao</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7837,7 +7837,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B75" t="n">
         <v>3</v>
@@ -7849,7 +7849,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -7865,7 +7865,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B76" t="n">
         <v>3</v>
@@ -7877,12 +7877,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>clima_ultimas_24h</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7893,7 +7893,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B77" t="n">
         <v>3</v>
@@ -7905,7 +7905,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>clima_ultimas_24h</t>
+          <t>clima</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -7921,7 +7921,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B78" t="n">
         <v>3</v>
@@ -7933,7 +7933,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>tipo_coleta</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -7949,7 +7949,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B79" t="n">
         <v>3</v>
@@ -7961,7 +7961,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>tipo_coleta</t>
+          <t>responsavel_amostra</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7977,7 +7977,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B80" t="n">
         <v>3</v>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>responsavel_amostra</t>
+          <t>planejamento_amostragem</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8005,7 +8005,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B81" t="n">
         <v>3</v>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>planejamento_amostragem</t>
+          <t>descricao_nao_conformidade</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8033,7 +8033,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B82" t="n">
         <v>3</v>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>descricao_nao_conformidade</t>
+          <t>codigo_laudo_substituido</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8061,19 +8061,19 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>codigo_laudo_substituido</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8089,7 +8089,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B84" t="n">
         <v>1</v>
@@ -8101,12 +8101,12 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8117,7 +8117,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B85" t="n">
         <v>1</v>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -8145,7 +8145,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B86" t="n">
         <v>1</v>
@@ -8157,12 +8157,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -8173,7 +8173,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B87" t="n">
         <v>1</v>
@@ -8185,12 +8185,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -8201,7 +8201,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B88" t="n">
         <v>1</v>
@@ -8213,12 +8213,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -8229,7 +8229,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B89" t="n">
         <v>1</v>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>proposta_comercial</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -8257,7 +8257,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B90" t="n">
         <v>1</v>
@@ -8269,7 +8269,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>proposta_comercial</t>
+          <t>cliente</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8285,7 +8285,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B91" t="n">
         <v>1</v>
@@ -8297,7 +8297,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>cliente</t>
+          <t>cnpj_cpf</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8313,7 +8313,7 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B92" t="n">
         <v>1</v>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>cnpj_cpf</t>
+          <t>contato</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8341,7 +8341,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B93" t="n">
         <v>1</v>
@@ -8353,7 +8353,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>contato</t>
+          <t>telefone</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8369,7 +8369,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B94" t="n">
         <v>1</v>
@@ -8381,7 +8381,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>telefone</t>
+          <t>endereco</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -8397,19 +8397,19 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B95" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>endereco</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8425,7 +8425,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B96" t="n">
         <v>5</v>
@@ -8437,12 +8437,12 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -8453,7 +8453,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B97" t="n">
         <v>5</v>
@@ -8465,12 +8465,12 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -8481,7 +8481,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B98" t="n">
         <v>5</v>
@@ -8493,12 +8493,12 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -8509,7 +8509,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B99" t="n">
         <v>5</v>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -8537,7 +8537,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B100" t="n">
         <v>5</v>
@@ -8549,12 +8549,12 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8565,7 +8565,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B101" t="n">
         <v>5</v>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>tabela_indice</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8593,7 +8593,7 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B102" t="n">
         <v>5</v>
@@ -8605,12 +8605,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>tabela_indice</t>
+          <t>categoria</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8621,7 +8621,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B103" t="n">
         <v>5</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>categoria</t>
+          <t>subcategoria</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8649,7 +8649,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B104" t="n">
         <v>5</v>
@@ -8661,7 +8661,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>subcategoria</t>
+          <t>tipo_registro</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -8677,7 +8677,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B105" t="n">
         <v>5</v>
@@ -8689,7 +8689,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>tipo_registro</t>
+          <t>modo_auditoria</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8705,7 +8705,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B106" t="n">
         <v>5</v>
@@ -8717,7 +8717,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>modo_auditoria</t>
+          <t>cabecalho_detectado</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -8733,7 +8733,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B107" t="n">
         <v>5</v>
@@ -8745,7 +8745,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>cabecalho_detectado</t>
+          <t>colunas_detectadas</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -8761,7 +8761,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B108" t="n">
         <v>5</v>
@@ -8773,7 +8773,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>colunas_detectadas</t>
+          <t>colunas_mapeadas</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8789,7 +8789,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B109" t="n">
         <v>5</v>
@@ -8801,7 +8801,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>colunas_mapeadas</t>
+          <t>colunas_sem_mapeamento</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8817,7 +8817,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B110" t="n">
         <v>5</v>
@@ -8829,7 +8829,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>colunas_sem_mapeamento</t>
+          <t>campos_esperados</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8845,7 +8845,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B111" t="n">
         <v>5</v>
@@ -8857,7 +8857,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>campos_esperados</t>
+          <t>campos_obrigatorios_ausentes</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8873,7 +8873,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B112" t="n">
         <v>5</v>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>campos_obrigatorios_ausentes</t>
+          <t>campos_opcionais_ausentes</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8901,7 +8901,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B113" t="n">
         <v>5</v>
@@ -8913,7 +8913,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>campos_opcionais_ausentes</t>
+          <t>usou_fallback</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8929,7 +8929,7 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B114" t="n">
         <v>5</v>
@@ -8941,7 +8941,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>usou_fallback</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -8957,7 +8957,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B115" t="n">
         <v>5</v>
@@ -8969,7 +8969,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>observacao</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8985,19 +8985,19 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B116" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>observacao</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -9013,7 +9013,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B117" t="n">
         <v>6</v>
@@ -9025,12 +9025,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -9041,7 +9041,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B118" t="n">
         <v>6</v>
@@ -9053,12 +9053,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -9069,7 +9069,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B119" t="n">
         <v>6</v>
@@ -9081,12 +9081,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -9097,7 +9097,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B120" t="n">
         <v>6</v>
@@ -9109,12 +9109,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -9125,7 +9125,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B121" t="n">
         <v>6</v>
@@ -9137,12 +9137,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>template_avaliado</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -9153,7 +9153,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B122" t="n">
         <v>6</v>
@@ -9165,12 +9165,12 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>template_avaliado</t>
+          <t>score</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -9181,7 +9181,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B123" t="n">
         <v>6</v>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>score_minimo</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -9209,7 +9209,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B124" t="n">
         <v>6</v>
@@ -9221,12 +9221,12 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>score_minimo</t>
+          <t>prioridade</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -9237,7 +9237,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B125" t="n">
         <v>6</v>
@@ -9249,12 +9249,12 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>prioridade</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -9265,7 +9265,7 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B126" t="n">
         <v>6</v>
@@ -9277,7 +9277,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>regras_encontradas</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -9293,24 +9293,24 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B127" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>regras_encontradas</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -9321,7 +9321,7 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B128" t="n">
         <v>7</v>
@@ -9333,12 +9333,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -9349,7 +9349,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B129" t="n">
         <v>7</v>
@@ -9361,12 +9361,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>row_number</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -9377,7 +9377,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B130" t="n">
         <v>7</v>
@@ -9389,7 +9389,7 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>row_number</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -9405,7 +9405,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B131" t="n">
         <v>7</v>
@@ -9417,12 +9417,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -9433,7 +9433,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B132" t="n">
         <v>7</v>
@@ -9445,7 +9445,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>field</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -9461,7 +9461,7 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B133" t="n">
         <v>7</v>
@@ -9473,7 +9473,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>field</t>
+          <t>error_type</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -9489,7 +9489,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B134" t="n">
         <v>7</v>
@@ -9501,7 +9501,7 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>error_type</t>
+          <t>message</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -9517,7 +9517,7 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B135" t="n">
         <v>7</v>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -9545,19 +9545,19 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B136" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -9573,7 +9573,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B137" t="n">
         <v>8</v>
@@ -9585,12 +9585,12 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -9601,7 +9601,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B138" t="n">
         <v>8</v>
@@ -9613,12 +9613,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -9629,7 +9629,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B139" t="n">
         <v>8</v>
@@ -9641,12 +9641,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -9657,7 +9657,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B140" t="n">
         <v>8</v>
@@ -9669,12 +9669,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -9685,7 +9685,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B141" t="n">
         <v>8</v>
@@ -9697,12 +9697,12 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -9713,7 +9713,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B142" t="n">
         <v>8</v>
@@ -9725,12 +9725,12 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -9741,7 +9741,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B143" t="n">
         <v>8</v>
@@ -9753,7 +9753,7 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>embalagem</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -9769,7 +9769,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B144" t="n">
         <v>8</v>
@@ -9781,7 +9781,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>embalagem</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9797,7 +9797,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B145" t="n">
         <v>8</v>
@@ -9809,7 +9809,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>preservacao</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -9825,7 +9825,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B146" t="n">
         <v>8</v>
@@ -9837,7 +9837,7 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>preservacao</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -9853,19 +9853,19 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B147" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9881,7 +9881,7 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B148" t="n">
         <v>9</v>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9909,7 +9909,7 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B149" t="n">
         <v>9</v>
@@ -9921,12 +9921,12 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9937,7 +9937,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B150" t="n">
         <v>9</v>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9965,7 +9965,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B151" t="n">
         <v>9</v>
@@ -9977,12 +9977,12 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9993,7 +9993,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B152" t="n">
         <v>9</v>
@@ -10005,12 +10005,12 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -10021,7 +10021,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B153" t="n">
         <v>9</v>
@@ -10033,7 +10033,7 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -10049,7 +10049,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B154" t="n">
         <v>9</v>
@@ -10061,12 +10061,12 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -10077,19 +10077,19 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B155" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -10105,7 +10105,7 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B156" t="n">
         <v>10</v>
@@ -10117,12 +10117,12 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -10133,7 +10133,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B157" t="n">
         <v>10</v>
@@ -10145,12 +10145,12 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -10161,7 +10161,7 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B158" t="n">
         <v>10</v>
@@ -10173,12 +10173,12 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -10189,7 +10189,7 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B159" t="n">
         <v>10</v>
@@ -10201,12 +10201,12 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -10217,7 +10217,7 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B160" t="n">
         <v>10</v>
@@ -10229,12 +10229,12 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -10245,7 +10245,7 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B161" t="n">
         <v>10</v>
@@ -10257,7 +10257,7 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -10273,7 +10273,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B162" t="n">
         <v>10</v>
@@ -10285,12 +10285,12 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -10301,19 +10301,19 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B163" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10329,7 +10329,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B164" t="n">
         <v>11</v>
@@ -10341,12 +10341,12 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -10357,7 +10357,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B165" t="n">
         <v>11</v>
@@ -10369,12 +10369,12 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -10385,7 +10385,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B166" t="n">
         <v>11</v>
@@ -10397,12 +10397,12 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -10413,7 +10413,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B167" t="n">
         <v>11</v>
@@ -10425,12 +10425,12 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -10441,7 +10441,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B168" t="n">
         <v>11</v>
@@ -10453,12 +10453,12 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -10469,7 +10469,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B169" t="n">
         <v>11</v>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -10497,7 +10497,7 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B170" t="n">
         <v>11</v>
@@ -10509,12 +10509,12 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -10525,19 +10525,19 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B171" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10553,7 +10553,7 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B172" t="n">
         <v>12</v>
@@ -10565,12 +10565,12 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -10581,7 +10581,7 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B173" t="n">
         <v>12</v>
@@ -10593,12 +10593,12 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -10609,7 +10609,7 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B174" t="n">
         <v>12</v>
@@ -10621,12 +10621,12 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -10637,7 +10637,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B175" t="n">
         <v>12</v>
@@ -10649,12 +10649,12 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -10665,7 +10665,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B176" t="n">
         <v>12</v>
@@ -10677,12 +10677,12 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -10693,7 +10693,7 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B177" t="n">
         <v>12</v>
@@ -10705,7 +10705,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10721,7 +10721,7 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B178" t="n">
         <v>12</v>
@@ -10733,12 +10733,12 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>chave_validacao</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -10749,19 +10749,19 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B179" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>chave_validacao</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -10777,7 +10777,7 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B180" t="n">
         <v>20</v>
@@ -10789,7 +10789,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>caminho_arquivo</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10805,7 +10805,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B181" t="n">
         <v>20</v>
@@ -10817,12 +10817,12 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>caminho_arquivo</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -10833,7 +10833,7 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B182" t="n">
         <v>20</v>
@@ -10845,12 +10845,12 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -10861,7 +10861,7 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B183" t="n">
         <v>20</v>
@@ -10873,12 +10873,12 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -10889,7 +10889,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B184" t="n">
         <v>20</v>
@@ -10901,12 +10901,12 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10917,7 +10917,7 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B185" t="n">
         <v>20</v>
@@ -10929,12 +10929,12 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -10945,7 +10945,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B186" t="n">
         <v>20</v>
@@ -10957,12 +10957,12 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10973,7 +10973,7 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B187" t="n">
         <v>20</v>
@@ -10985,12 +10985,12 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>data_publicacao</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -11001,7 +11001,7 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B188" t="n">
         <v>20</v>
@@ -11013,7 +11013,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>data_publicacao</t>
+          <t>data_coleta</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -11029,7 +11029,7 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B189" t="n">
         <v>20</v>
@@ -11041,12 +11041,12 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>hash_arquivo</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
@@ -11057,7 +11057,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B190" t="n">
         <v>20</v>
@@ -11069,7 +11069,7 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>hash_arquivo</t>
+          <t>hash_texto</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -11085,7 +11085,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B191" t="n">
         <v>20</v>
@@ -11097,7 +11097,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>hash_texto</t>
+          <t>grupo_duplicidade</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11113,7 +11113,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B192" t="n">
         <v>20</v>
@@ -11125,7 +11125,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>grupo_duplicidade</t>
+          <t>tipo_duplicidade</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -11141,7 +11141,7 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B193" t="n">
         <v>20</v>
@@ -11153,7 +11153,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>tipo_duplicidade</t>
+          <t>arquivo_referencia</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11169,7 +11169,7 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B194" t="n">
         <v>20</v>
@@ -11181,7 +11181,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>arquivo_referencia</t>
+          <t>motivo</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11197,7 +11197,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B195" t="n">
         <v>20</v>
@@ -11209,7 +11209,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>motivo</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11225,19 +11225,19 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B196" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11253,7 +11253,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B197" t="n">
         <v>21</v>
@@ -11265,12 +11265,12 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -11281,7 +11281,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B198" t="n">
         <v>21</v>
@@ -11293,12 +11293,12 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -11309,7 +11309,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B199" t="n">
         <v>21</v>
@@ -11321,12 +11321,12 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -11337,7 +11337,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B200" t="n">
         <v>21</v>
@@ -11349,12 +11349,12 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
@@ -11365,7 +11365,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B201" t="n">
         <v>21</v>
@@ -11377,12 +11377,12 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -11393,7 +11393,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B202" t="n">
         <v>21</v>
@@ -11405,7 +11405,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>tabela_indice</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -11421,7 +11421,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B203" t="n">
         <v>21</v>
@@ -11433,12 +11433,12 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>tabela_indice</t>
+          <t>objeto_tipo</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -11449,7 +11449,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B204" t="n">
         <v>21</v>
@@ -11461,7 +11461,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>objeto_tipo</t>
+          <t>secao</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -11477,7 +11477,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B205" t="n">
         <v>21</v>
@@ -11489,7 +11489,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>secao</t>
+          <t>titulo_detectado</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -11505,7 +11505,7 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B206" t="n">
         <v>21</v>
@@ -11517,7 +11517,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>titulo_detectado</t>
+          <t>modo_auditoria</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -11533,7 +11533,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B207" t="n">
         <v>21</v>
@@ -11545,7 +11545,7 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>modo_auditoria</t>
+          <t>regra_encontrada</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -11561,7 +11561,7 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B208" t="n">
         <v>21</v>
@@ -11573,12 +11573,12 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>regra_encontrada</t>
+          <t>ocorrencias_detectadas</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -11589,7 +11589,7 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B209" t="n">
         <v>21</v>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>ocorrencias_detectadas</t>
+          <t>registros_extraidos</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -11617,7 +11617,7 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B210" t="n">
         <v>21</v>
@@ -11629,12 +11629,12 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>registros_extraidos</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -11645,7 +11645,7 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B211" t="n">
         <v>21</v>
@@ -11657,7 +11657,7 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>observacao</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -11666,34 +11666,6 @@
         </is>
       </c>
       <c r="F211" t="inlineStr">
-        <is>
-          <t>sim</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="n">
-        <v>293</v>
-      </c>
-      <c r="B212" t="n">
-        <v>21</v>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>section_extraction_audit</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>observacao</t>
-        </is>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr">
         <is>
           <t>sim</t>
         </is>

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G144"/>
+  <dimension ref="A1:G147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1288,7 +1288,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Observa..es:\s*(.*?)(?:\s+Latitude:|\n)</t>
+          <t>Observa..es:\s*(.*?)(?=\s+(?:Condi..es\s+clim.ticas\s+nas\s+.ltimas\s+24\s+horas:|Condi..es\s+clim.ticas\s+no\s+momento\s+da\s+coleta:|Local\s+da\s+Coleta:|Tipo\s+de\s+Coleta:|Responsabilidade\s+da\s+Amostragem:|Descri..o\s+da\s+n.o-conformidade:|Planejamento\s+de\s+Amostragem:|Latitude(?:\s*\(coordenada\s+real\))?:|Longitude(?:\s*\(coordenada\s+real\))?:)|\n|$)</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>clima_ultimas_24h</t>
+          <t>condicoes_climaticas_nas_ultimas_24_horas</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>condicoes_climaticas_no_momento_da_coleta</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Condi..es clim.ticas no momento da coleta:\s*(.*?)(?:\s+Local da Coleta:|\n)</t>
+          <t>Condi..es\s+clim.ticas\s+no\s+momento\s+da\s+coleta:\s*(.*?)(?=\s+(?:Local\s+da\s+Coleta:|Tipo\s+de\s+Coleta:|Responsabilidade\s+da\s+Amostragem:|Descri..o\s+da\s+n.o-conformidade:|Planejamento\s+de\s+Amostragem:|Latitude(?:\s*\(coordenada\s+real\))?:|Longitude(?:\s*\(coordenada\s+real\))?:)|\n|$)</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>(?:^|\n)\s*Considera..es\s+Gerais\s*:?\s*(.*?)(?=\n\s*(?:Declara..o\s+de\s+Conformidade|Chave\s+de\s+Valida..o|Notas?|$))</t>
+          <t>(?:^|\n)[ \t]*Considera..es\s+Gerais[ \t]*:?[ \t]*(?:\n|$)(.*?)(?=\n[ \t]*(?:Declara..o\s+de\s+Conformidade|Chave\s+de\s+Valida..o|Notas?|Embalagens\s+e\s+Preservantes|Registro\s+da\s+Coleta|FO-ANL-\d+|Revis.o\s*:|CEP\s*:|Aprova..o\s*:)|\Z)</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>descricao=Extrai o bloco textual de Consideracoes Gerais.</t>
+          <t>descricao=Extrai integralmente general_considerations ate a proxima secao ou rodape.</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>(?:^|\n)\s*Declara..o\s+de\s+Conformidade\s*:?\s*(.*?)(?=\n\s*(?:Chave\s+de\s+Valida..o|Considera..es\s+Gerais|Notas?|$))</t>
+          <t>(?:^|\n)[ \t]*Declara..o\s+de\s+Conformidade[ \t]*:?[ \t]*(?:\([^\n]*\))?[ \t]*(?:\n|$)(.*?)(?=\n[ \t]*(?:Chave\s+de\s+Valida..o|Considera..es\s+Gerais|Notas?|Embalagens\s+e\s+Preservantes|Registro\s+da\s+Coleta|FO-ANL-\d+|Revis.o\s*:|CEP\s*:|Aprova..o\s*:)|\Z)</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>descricao=Extrai o bloco textual de Declaracao de Conformidade.</t>
+          <t>descricao=Extrai integralmente conformity_statement ate a proxima secao ou rodape.</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -5312,6 +5312,105 @@
       <c r="G144" t="inlineStr">
         <is>
           <t>N?o se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>147</v>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>validation_key</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>audit_ignore</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>(?:^|\n)[ \t]*Chave\s+de\s+Valida..o\s*:?\s*\n?[ \t]*FO-ANL-\d+\b</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>descricao=Ignora codigo de formulario apresentado sem chave de validacao.</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>N?o se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>148</v>
+      </c>
+      <c r="B146" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>latitude_real</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Latitude\s*\(coordenada\s+real\)\s*:\s*([+-]?\d+(?:[.,]\d+)?)</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>149</v>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>longitude_real</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Longitude\s*\(coordenada\s+real\)\s*:\s*([+-]?\d+(?:[.,]\d+)?)</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
         </is>
       </c>
     </row>
@@ -5327,7 +5426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="13.54296875" customWidth="1" min="1" max="1"/>
@@ -5731,6 +5830,24 @@
         </is>
       </c>
       <c r="D22" t="inlineStr">
+        <is>
+          <t>Verdadeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>field_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
         <is>
           <t>Verdadeiro</t>
         </is>
@@ -5748,7 +5865,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F211"/>
+  <dimension ref="A1:F227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9.7265625" customWidth="1" min="1" max="1"/>
@@ -7417,14 +7534,14 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>141</v>
+        <v>167</v>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -7445,14 +7562,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>142</v>
+        <v>168</v>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -7473,14 +7590,14 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -7501,14 +7618,14 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="B63" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -7529,14 +7646,14 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -7557,14 +7674,14 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>146</v>
+        <v>172</v>
       </c>
       <c r="B65" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -7585,19 +7702,19 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="B66" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>proposta_comercial</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -7613,19 +7730,19 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>148</v>
+        <v>174</v>
       </c>
       <c r="B67" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>tipo_amostra</t>
+          <t>cliente</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -7641,19 +7758,19 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>149</v>
+        <v>175</v>
       </c>
       <c r="B68" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>criterio_conformidade</t>
+          <t>cnpj_cpf</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -7669,24 +7786,24 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>150</v>
+        <v>176</v>
       </c>
       <c r="B69" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>contato</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -7697,24 +7814,24 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>151</v>
+        <v>177</v>
       </c>
       <c r="B70" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>data_publicacao</t>
+          <t>telefone</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -7725,24 +7842,24 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>152</v>
+        <v>178</v>
       </c>
       <c r="B71" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>client</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>data_recebimento</t>
+          <t>endereco</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -7753,19 +7870,19 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>153</v>
+        <v>179</v>
       </c>
       <c r="B72" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>observacoes</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -7781,24 +7898,24 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="B73" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>localizacao</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -7809,24 +7926,24 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>156</v>
+        <v>181</v>
       </c>
       <c r="B74" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>latitude</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -7837,24 +7954,24 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>157</v>
+        <v>182</v>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>longitude</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -7865,24 +7982,24 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="B76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>clima_ultimas_24h</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -7893,24 +8010,24 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>159</v>
+        <v>184</v>
       </c>
       <c r="B77" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>clima</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -7921,24 +8038,24 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>160</v>
+        <v>185</v>
       </c>
       <c r="B78" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>tipo_coleta</t>
+          <t>tabela_indice</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -7949,19 +8066,19 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>responsavel_amostra</t>
+          <t>categoria</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -7977,19 +8094,19 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>162</v>
+        <v>187</v>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>planejamento_amostragem</t>
+          <t>subcategoria</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -8005,19 +8122,19 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>163</v>
+        <v>188</v>
       </c>
       <c r="B81" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>descricao_nao_conformidade</t>
+          <t>tipo_registro</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -8033,19 +8150,19 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>164</v>
+        <v>189</v>
       </c>
       <c r="B82" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>sample</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>codigo_laudo_substituido</t>
+          <t>modo_auditoria</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -8061,19 +8178,19 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>165</v>
+        <v>190</v>
       </c>
       <c r="B83" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>cabecalho_detectado</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -8089,24 +8206,24 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>166</v>
+        <v>191</v>
       </c>
       <c r="B84" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>colunas_detectadas</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -8117,19 +8234,19 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="B85" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>colunas_mapeadas</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -8145,24 +8262,24 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="B86" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>colunas_sem_mapeamento</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -8173,24 +8290,24 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>169</v>
+        <v>194</v>
       </c>
       <c r="B87" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>campos_esperados</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -8201,24 +8318,24 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>170</v>
+        <v>195</v>
       </c>
       <c r="B88" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>campos_obrigatorios_ausentes</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -8229,19 +8346,19 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>171</v>
+        <v>196</v>
       </c>
       <c r="B89" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>proposta_comercial</t>
+          <t>campos_opcionais_ausentes</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -8257,19 +8374,19 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>172</v>
+        <v>197</v>
       </c>
       <c r="B90" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>cliente</t>
+          <t>usou_fallback</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -8285,19 +8402,19 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>173</v>
+        <v>198</v>
       </c>
       <c r="B91" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>cnpj_cpf</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -8313,19 +8430,19 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="B92" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>table_extraction_audit</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>contato</t>
+          <t>observacao</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -8341,19 +8458,19 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="B93" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>telefone</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -8369,24 +8486,24 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="B94" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>client</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>endereco</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -8397,19 +8514,19 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>177</v>
+        <v>202</v>
       </c>
       <c r="B95" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -8425,19 +8542,19 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="B96" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -8453,24 +8570,24 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>179</v>
+        <v>204</v>
       </c>
       <c r="B97" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -8481,24 +8598,24 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>180</v>
+        <v>205</v>
       </c>
       <c r="B98" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>template_avaliado</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -8509,24 +8626,24 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>181</v>
+        <v>206</v>
       </c>
       <c r="B99" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>score</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -8537,24 +8654,24 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>182</v>
+        <v>207</v>
       </c>
       <c r="B100" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>score_minimo</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8565,19 +8682,19 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>183</v>
+        <v>208</v>
       </c>
       <c r="B101" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>tabela_indice</t>
+          <t>prioridade</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -8593,19 +8710,19 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>184</v>
+        <v>209</v>
       </c>
       <c r="B102" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>categoria</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -8621,19 +8738,19 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>185</v>
+        <v>210</v>
       </c>
       <c r="B103" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>classification_audit</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>subcategoria</t>
+          <t>regras_encontradas</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -8649,24 +8766,24 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>186</v>
+        <v>211</v>
       </c>
       <c r="B104" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>tipo_registro</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8677,19 +8794,19 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>187</v>
+        <v>212</v>
       </c>
       <c r="B105" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>modo_auditoria</t>
+          <t>sheet</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -8705,24 +8822,24 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="B106" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>cabecalho_detectado</t>
+          <t>row_number</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -8733,24 +8850,24 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>189</v>
+        <v>214</v>
       </c>
       <c r="B107" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>colunas_detectadas</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -8761,19 +8878,19 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>190</v>
+        <v>215</v>
       </c>
       <c r="B108" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>colunas_mapeadas</t>
+          <t>parameter</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -8789,19 +8906,19 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>191</v>
+        <v>216</v>
       </c>
       <c r="B109" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>colunas_sem_mapeamento</t>
+          <t>field</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -8817,19 +8934,19 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>192</v>
+        <v>217</v>
       </c>
       <c r="B110" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>campos_esperados</t>
+          <t>error_type</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -8845,19 +8962,19 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>193</v>
+        <v>218</v>
       </c>
       <c r="B111" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>campos_obrigatorios_ausentes</t>
+          <t>message</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -8873,19 +8990,19 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="B112" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>validation_errors</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>campos_opcionais_ausentes</t>
+          <t>value</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -8901,19 +9018,19 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="B113" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>usou_fallback</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -8929,24 +9046,24 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>196</v>
+        <v>221</v>
       </c>
       <c r="B114" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -8957,19 +9074,19 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="B115" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>table_extraction_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>observacao</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -8985,24 +9102,24 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="B116" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -9013,24 +9130,24 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="B117" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -9041,24 +9158,24 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>200</v>
+        <v>225</v>
       </c>
       <c r="B118" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -9069,24 +9186,24 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="B119" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -9097,24 +9214,24 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="B120" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>embalagem</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -9125,19 +9242,19 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>203</v>
+        <v>228</v>
       </c>
       <c r="B121" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>template_avaliado</t>
+          <t>volume</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -9153,24 +9270,24 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>204</v>
+        <v>229</v>
       </c>
       <c r="B122" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>preservacao</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -9181,24 +9298,24 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="B123" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>packaging_preservatives</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>score_minimo</t>
+          <t>metodos</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -9209,24 +9326,24 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>206</v>
+        <v>231</v>
       </c>
       <c r="B124" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>prioridade</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -9237,24 +9354,24 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>207</v>
+        <v>232</v>
       </c>
       <c r="B125" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -9265,19 +9382,19 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>208</v>
+        <v>233</v>
       </c>
       <c r="B126" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>classification_audit</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>regras_encontradas</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -9293,24 +9410,24 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>209</v>
+        <v>234</v>
       </c>
       <c r="B127" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -9321,24 +9438,24 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>210</v>
+        <v>235</v>
       </c>
       <c r="B128" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>sheet</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -9349,19 +9466,19 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>211</v>
+        <v>236</v>
       </c>
       <c r="B129" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>row_number</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -9377,19 +9494,19 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="B130" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -9405,19 +9522,19 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>213</v>
+        <v>238</v>
       </c>
       <c r="B131" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>parameter</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -9433,19 +9550,19 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="B132" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>field</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -9461,24 +9578,24 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>215</v>
+        <v>240</v>
       </c>
       <c r="B133" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>error_type</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -9489,19 +9606,19 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>216</v>
+        <v>241</v>
       </c>
       <c r="B134" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -9517,24 +9634,24 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="B135" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>validation_errors</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -9545,24 +9662,24 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>218</v>
+        <v>243</v>
       </c>
       <c r="B136" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -9573,19 +9690,19 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>219</v>
+        <v>244</v>
       </c>
       <c r="B137" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -9601,24 +9718,24 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>220</v>
+        <v>245</v>
       </c>
       <c r="B138" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -9629,24 +9746,24 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="B139" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>general_considerations</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -9657,24 +9774,24 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>222</v>
+        <v>247</v>
       </c>
       <c r="B140" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -9685,19 +9802,19 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="B141" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -9713,19 +9830,19 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="B142" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -9741,24 +9858,24 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="B143" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>embalagem</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -9769,24 +9886,24 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="B144" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>volume</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -9797,24 +9914,24 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>227</v>
+        <v>252</v>
       </c>
       <c r="B145" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>preservacao</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -9825,24 +9942,24 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>228</v>
+        <v>253</v>
       </c>
       <c r="B146" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>packaging_preservatives</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>metodos</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -9853,19 +9970,19 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>229</v>
+        <v>254</v>
       </c>
       <c r="B147" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>conformity_statement</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -9881,24 +9998,24 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>230</v>
+        <v>255</v>
       </c>
       <c r="B148" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -9909,24 +10026,24 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>231</v>
+        <v>256</v>
       </c>
       <c r="B149" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -9937,24 +10054,24 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>232</v>
+        <v>257</v>
       </c>
       <c r="B150" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -9965,24 +10082,24 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>233</v>
+        <v>258</v>
       </c>
       <c r="B151" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -9993,24 +10110,24 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>234</v>
+        <v>259</v>
       </c>
       <c r="B152" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -10021,19 +10138,19 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>235</v>
+        <v>260</v>
       </c>
       <c r="B153" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -10049,24 +10166,24 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>236</v>
+        <v>261</v>
       </c>
       <c r="B154" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -10077,19 +10194,19 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>237</v>
+        <v>262</v>
       </c>
       <c r="B155" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>validation_key</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>chave_validacao</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -10105,24 +10222,24 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>238</v>
+        <v>263</v>
       </c>
       <c r="B156" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -10133,19 +10250,19 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>239</v>
+        <v>264</v>
       </c>
       <c r="B157" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>caminho_arquivo</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -10161,19 +10278,19 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>240</v>
+        <v>265</v>
       </c>
       <c r="B158" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -10189,24 +10306,24 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>241</v>
+        <v>266</v>
       </c>
       <c r="B159" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -10217,19 +10334,19 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>242</v>
+        <v>267</v>
       </c>
       <c r="B160" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -10245,24 +10362,24 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>243</v>
+        <v>268</v>
       </c>
       <c r="B161" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -10273,24 +10390,24 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>244</v>
+        <v>269</v>
       </c>
       <c r="B162" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>general_considerations</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -10301,19 +10418,19 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>245</v>
+        <v>270</v>
       </c>
       <c r="B163" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -10329,24 +10446,24 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="B164" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>data_publicacao</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -10357,24 +10474,24 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>247</v>
+        <v>272</v>
       </c>
       <c r="B165" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>data_coleta</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -10385,24 +10502,24 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>248</v>
+        <v>273</v>
       </c>
       <c r="B166" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>hash_arquivo</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -10413,24 +10530,24 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>249</v>
+        <v>274</v>
       </c>
       <c r="B167" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>hash_texto</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -10441,24 +10558,24 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>250</v>
+        <v>275</v>
       </c>
       <c r="B168" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>grupo_duplicidade</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -10469,24 +10586,24 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>251</v>
+        <v>276</v>
       </c>
       <c r="B169" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>tipo_duplicidade</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -10497,19 +10614,19 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>252</v>
+        <v>277</v>
       </c>
       <c r="B170" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>conformity_statement</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>arquivo_referencia</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -10525,19 +10642,19 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="B171" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>motivo</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -10553,24 +10670,24 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>254</v>
+        <v>279</v>
       </c>
       <c r="B172" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>duplicate_audit</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -10581,19 +10698,19 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>255</v>
+        <v>280</v>
       </c>
       <c r="B173" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -10609,19 +10726,19 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>256</v>
+        <v>281</v>
       </c>
       <c r="B174" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -10637,24 +10754,24 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>257</v>
+        <v>282</v>
       </c>
       <c r="B175" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -10665,19 +10782,19 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>258</v>
+        <v>283</v>
       </c>
       <c r="B176" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10693,24 +10810,24 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="B177" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -10721,24 +10838,24 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>260</v>
+        <v>285</v>
       </c>
       <c r="B178" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>validation_key</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>chave_validacao</t>
+          <t>pagina</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -10749,24 +10866,24 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>261</v>
+        <v>286</v>
       </c>
       <c r="B179" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>tabela_indice</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -10777,19 +10894,19 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="B180" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>caminho_arquivo</t>
+          <t>objeto_tipo</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -10805,24 +10922,24 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="B181" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>secao</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -10833,19 +10950,19 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>264</v>
+        <v>289</v>
       </c>
       <c r="B182" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>titulo_detectado</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -10861,24 +10978,24 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>265</v>
+        <v>290</v>
       </c>
       <c r="B183" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>modo_auditoria</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -10889,24 +11006,24 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="B184" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>regra_encontrada</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -10917,19 +11034,19 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>267</v>
+        <v>292</v>
       </c>
       <c r="B185" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>id_amostra</t>
+          <t>ocorrencias_detectadas</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -10945,24 +11062,24 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>268</v>
+        <v>293</v>
       </c>
       <c r="B186" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>identificacao_amostra</t>
+          <t>registros_extraidos</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -10973,24 +11090,24 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>269</v>
+        <v>294</v>
       </c>
       <c r="B187" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>data_publicacao</t>
+          <t>status</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -11001,24 +11118,24 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>270</v>
+        <v>295</v>
       </c>
       <c r="B188" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>section_extraction_audit</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>data_coleta</t>
+          <t>observacao</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>data_hora</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
@@ -11029,19 +11146,19 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>271</v>
+        <v>141</v>
       </c>
       <c r="B189" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>hash_arquivo</t>
+          <t>nome_do_arquivo</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11057,24 +11174,24 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>272</v>
+        <v>142</v>
       </c>
       <c r="B190" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>hash_texto</t>
+          <t>id_taxonomia</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
@@ -11085,19 +11202,19 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>273</v>
+        <v>143</v>
       </c>
       <c r="B191" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>grupo_duplicidade</t>
+          <t>nome_taxonomia</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -11113,24 +11230,24 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>274</v>
+        <v>144</v>
       </c>
       <c r="B192" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>tipo_duplicidade</t>
+          <t>versao_template</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
@@ -11141,24 +11258,24 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>275</v>
+        <v>145</v>
       </c>
       <c r="B193" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>arquivo_referencia</t>
+          <t>acm_data_hora_extracao</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
@@ -11169,24 +11286,24 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>276</v>
+        <v>146</v>
       </c>
       <c r="B194" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>motivo</t>
+          <t>id_amostra</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>inteiro</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
@@ -11197,19 +11314,19 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>277</v>
+        <v>147</v>
       </c>
       <c r="B195" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>duplicate_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>identificacao_amostra</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -11225,19 +11342,19 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>278</v>
+        <v>148</v>
       </c>
       <c r="B196" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>nome_do_arquivo</t>
+          <t>tipo_amostra</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -11253,24 +11370,24 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>279</v>
+        <v>149</v>
       </c>
       <c r="B197" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>id_taxonomia</t>
+          <t>criterio_conformidade</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -11281,24 +11398,24 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>280</v>
+        <v>150</v>
       </c>
       <c r="B198" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>nome_taxonomia</t>
+          <t>data_coleta</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -11309,24 +11426,24 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>281</v>
+        <v>151</v>
       </c>
       <c r="B199" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>versao_template</t>
+          <t>data_publicacao</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>data_hora</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -11337,19 +11454,19 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>282</v>
+        <v>152</v>
       </c>
       <c r="B200" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>acm_data_hora_extracao</t>
+          <t>data_recebimento</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -11365,24 +11482,24 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>283</v>
+        <v>153</v>
       </c>
       <c r="B201" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>pagina</t>
+          <t>observacoes</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
@@ -11393,24 +11510,24 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>284</v>
+        <v>155</v>
       </c>
       <c r="B202" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>tabela_indice</t>
+          <t>localizacao</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
@@ -11421,24 +11538,24 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>285</v>
+        <v>156</v>
       </c>
       <c r="B203" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>objeto_tipo</t>
+          <t>latitude</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
@@ -11449,24 +11566,24 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>286</v>
+        <v>157</v>
       </c>
       <c r="B204" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>secao</t>
+          <t>longitude</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -11477,24 +11594,24 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>287</v>
+        <v>158</v>
       </c>
       <c r="B205" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>titulo_detectado</t>
+          <t>latitude_real</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -11505,24 +11622,24 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>288</v>
+        <v>159</v>
       </c>
       <c r="B206" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>modo_auditoria</t>
+          <t>longitude_real</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>texto</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
@@ -11533,19 +11650,19 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>289</v>
+        <v>160</v>
       </c>
       <c r="B207" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>regra_encontrada</t>
+          <t>condicoes_climaticas_nas_ultimas_24_horas</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -11561,24 +11678,24 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>290</v>
+        <v>161</v>
       </c>
       <c r="B208" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>ocorrencias_detectadas</t>
+          <t>condicoes_climaticas_no_momento_da_coleta</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
@@ -11589,24 +11706,24 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>291</v>
+        <v>162</v>
       </c>
       <c r="B209" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>registros_extraidos</t>
+          <t>tipo_coleta</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>inteiro</t>
+          <t>texto</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -11617,19 +11734,19 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>292</v>
+        <v>163</v>
       </c>
       <c r="B210" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>responsavel_amostra</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -11645,27 +11762,475 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>293</v>
+        <v>164</v>
       </c>
       <c r="B211" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>section_extraction_audit</t>
+          <t>sample</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
+          <t>planejamento_amostragem</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="n">
+        <v>165</v>
+      </c>
+      <c r="B212" t="n">
+        <v>3</v>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>descricao_nao_conformidade</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="n">
+        <v>166</v>
+      </c>
+      <c r="B213" t="n">
+        <v>3</v>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>sample</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>codigo_laudo_substituido</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="n">
+        <v>296</v>
+      </c>
+      <c r="B214" t="n">
+        <v>22</v>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>field_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="n">
+        <v>297</v>
+      </c>
+      <c r="B215" t="n">
+        <v>22</v>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>field_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="n">
+        <v>298</v>
+      </c>
+      <c r="B216" t="n">
+        <v>22</v>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>field_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="n">
+        <v>299</v>
+      </c>
+      <c r="B217" t="n">
+        <v>22</v>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>field_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>versao_template</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="n">
+        <v>300</v>
+      </c>
+      <c r="B218" t="n">
+        <v>22</v>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>field_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>acm_data_hora_extracao</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>data_hora</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="n">
+        <v>301</v>
+      </c>
+      <c r="B219" t="n">
+        <v>22</v>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>field_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>schema_origem</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="n">
+        <v>302</v>
+      </c>
+      <c r="B220" t="n">
+        <v>22</v>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>field_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>campo</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="n">
+        <v>303</v>
+      </c>
+      <c r="B221" t="n">
+        <v>22</v>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>field_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>pagina</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="n">
+        <v>304</v>
+      </c>
+      <c r="B222" t="n">
+        <v>22</v>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>field_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>regra_encontrada</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="n">
+        <v>305</v>
+      </c>
+      <c r="B223" t="n">
+        <v>22</v>
+      </c>
+      <c r="C223" t="inlineStr">
+        <is>
+          <t>field_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D223" t="inlineStr">
+        <is>
+          <t>ocorrencias_detectadas</t>
+        </is>
+      </c>
+      <c r="E223" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="n">
+        <v>306</v>
+      </c>
+      <c r="B224" t="n">
+        <v>22</v>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>field_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D224" t="inlineStr">
+        <is>
+          <t>valor_extraido</t>
+        </is>
+      </c>
+      <c r="E224" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="n">
+        <v>307</v>
+      </c>
+      <c r="B225" t="n">
+        <v>22</v>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>field_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>campos_detectados_no_valor</t>
+        </is>
+      </c>
+      <c r="E225" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="n">
+        <v>308</v>
+      </c>
+      <c r="B226" t="n">
+        <v>22</v>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>field_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E226" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="n">
+        <v>309</v>
+      </c>
+      <c r="B227" t="n">
+        <v>22</v>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>field_extraction_audit</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
           <t>observacao</t>
         </is>
       </c>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>texto</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr">
+      <c r="E227" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
         <is>
           <t>sim</t>
         </is>

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G147"/>
+  <dimension ref="A1:G154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5414,6 +5414,237 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>150</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>revision_reason</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>section_start</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>(?:^|\n)\s*Motivo\s+da\s+Revis.o\s*:?\s*</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>descricao=Titulo da secao de motivo da revisao</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Nao se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>151</v>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>revision_reason</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>motivo_revisao</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Motivo\s+da\s+Revis.o\s*:?\s*\n\s*(Revis.o\s+\d+\s*-\s*[^\n]+)</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>descricao=Texto original do motivo da revisao</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Nao se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>152</v>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>section_discovery_ignore</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>method_reference</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>^ABNT\s+NBR$</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>descricao=Referencia de metodo, nao e titulo de secao</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Nao se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>153</v>
+      </c>
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>section_discovery_ignore</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>normative_table</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>^Tabela\s+(?:IV|VII)$</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>descricao=Referencia de tabela normativa</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Nao se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>154</v>
+      </c>
+      <c r="B152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>section_discovery_ignore</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>external_laboratory</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>^M.rieux\s+Nutrisciences$</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>descricao=Nome de laboratorio externo</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Nao se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>155</v>
+      </c>
+      <c r="B153" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>section_discovery_ignore</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>preservative_fragment</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>^(?:Frasco\s+Tiossulfato|Est.ril\s+de\s+S.dio|Acetato\s+de)$</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>descricao=Fragmento da tabela de embalagens e preservantes</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Nao se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>156</v>
+      </c>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>section_discovery_ignore</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>parameter_fragment</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>^(?:Alum.nio\s+Dissolvido,\s+Cor\s+Verdadeira,\s+Ferro\s+Dissolvido|Alum.nio\s+Dissolvido,\s+Ferro\s+Dissolvido|Dissolvido,\s+Cor\s+Verdadeira,\s+Ferro\s+Dissolvido|Verdadeira,\s+Ferro\s+Dissolvido|Mangan.s\s+Total)$</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>descricao=Parametro ou fragmento de lista de parametros</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Nao se aplica</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:G137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5426,7 +5657,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="13.54296875" customWidth="1" min="1" max="1"/>
@@ -5850,6 +6081,42 @@
       <c r="D23" t="inlineStr">
         <is>
           <t>Verdadeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>revision_reason</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Verdadeiro</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>section_discovery_ignore</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Falso</t>
         </is>
       </c>
     </row>
@@ -5865,7 +6132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F227"/>
+  <dimension ref="A1:F235"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9.7265625" customWidth="1" min="1" max="1"/>
@@ -12236,6 +12503,230 @@
         </is>
       </c>
     </row>
+    <row r="228">
+      <c r="A228" t="n">
+        <v>310</v>
+      </c>
+      <c r="B228" t="n">
+        <v>23</v>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>revision_reason</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E228" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="n">
+        <v>311</v>
+      </c>
+      <c r="B229" t="n">
+        <v>23</v>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>revision_reason</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E229" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="n">
+        <v>312</v>
+      </c>
+      <c r="B230" t="n">
+        <v>23</v>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>revision_reason</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="n">
+        <v>313</v>
+      </c>
+      <c r="B231" t="n">
+        <v>23</v>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>revision_reason</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>versao_template</t>
+        </is>
+      </c>
+      <c r="E231" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>314</v>
+      </c>
+      <c r="B232" t="n">
+        <v>23</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>revision_reason</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>acm_data_hora_extracao</t>
+        </is>
+      </c>
+      <c r="E232" t="inlineStr">
+        <is>
+          <t>data_hora</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>315</v>
+      </c>
+      <c r="B233" t="n">
+        <v>23</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>revision_reason</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>id_amostra</t>
+        </is>
+      </c>
+      <c r="E233" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>316</v>
+      </c>
+      <c r="B234" t="n">
+        <v>23</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>revision_reason</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>pagina</t>
+        </is>
+      </c>
+      <c r="E234" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>317</v>
+      </c>
+      <c r="B235" t="n">
+        <v>23</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>revision_reason</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>motivo_revisao</t>
+        </is>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G154"/>
+  <dimension ref="A1:G156"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5640,6 +5640,72 @@
         </is>
       </c>
       <c r="G154" t="inlineStr">
+        <is>
+          <t>Nao se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="n">
+        <v>157</v>
+      </c>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>container_value</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>^(?:Polietileno|Frasco\s+Est.ril|Vidro\s+.mbar|Vial)$</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>descricao=Valores reconhecidos como recipientes de embalagem</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Nao se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="n">
+        <v>158</v>
+      </c>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>volume_value</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>^\d+(?:[,.]\d+)?\s*mL$</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>descricao=Formato esperado do volume da embalagem</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
         <is>
           <t>Nao se aplica</t>
         </is>

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -594,7 +594,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G156"/>
+  <dimension ref="A1:G158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5466,7 +5466,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Motivo\s+da\s+Revis.o\s*:?\s*\n\s*(Revis.o\s+\d+\s*-\s*[^\n]+)</t>
+          <t>Motivo\s+da\s+Revis.o\s*:?\s*\n\s*(Revis.o\s+\d+\s*(?:-|:)\s*[^\n]+)</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5706,6 +5706,72 @@
         </is>
       </c>
       <c r="G156" t="inlineStr">
+        <is>
+          <t>Nao se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="n">
+        <v>159</v>
+      </c>
+      <c r="B157" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>packaging_preservatives</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>audit_ignore</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Embalagens\s+e\s+Preservantes.*?Embalagem\s+Volume\s+Preserva..o\s+M.todos\s*FO-ANL-\d+</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>descricao=Secao de embalagens presente sem linhas de dados</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Nao se aplica</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="n">
+        <v>160</v>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>revision_reason</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>audit_ignore</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Motivo\s+da\s+Revis.o\s*:?\s*(?:\n\s*)?FO-ANL-\d+</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>descricao=Secao de motivo da revisao presente sem texto</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
         <is>
           <t>Nao se aplica</t>
         </is>

--- a/config/taxonomy.xlsx
+++ b/config/taxonomy.xlsx
@@ -5789,7 +5789,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="13.54296875" customWidth="1" min="1" max="1"/>
@@ -6249,6 +6249,24 @@
       <c r="D25" t="inlineStr">
         <is>
           <t>Falso</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Verdadeiro</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F235"/>
+  <dimension ref="A1:F256"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="9.7265625" customWidth="1" min="1" max="1"/>
@@ -12859,6 +12877,594 @@
         </is>
       </c>
     </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>318</v>
+      </c>
+      <c r="B236" t="n">
+        <v>25</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>nome_do_arquivo</t>
+        </is>
+      </c>
+      <c r="E236" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>319</v>
+      </c>
+      <c r="B237" t="n">
+        <v>25</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>id_taxonomia</t>
+        </is>
+      </c>
+      <c r="E237" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>320</v>
+      </c>
+      <c r="B238" t="n">
+        <v>25</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>nome_taxonomia</t>
+        </is>
+      </c>
+      <c r="E238" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>321</v>
+      </c>
+      <c r="B239" t="n">
+        <v>25</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>versao_template</t>
+        </is>
+      </c>
+      <c r="E239" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>322</v>
+      </c>
+      <c r="B240" t="n">
+        <v>25</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>acm_data_hora_extracao</t>
+        </is>
+      </c>
+      <c r="E240" t="inlineStr">
+        <is>
+          <t>data_hora</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>323</v>
+      </c>
+      <c r="B241" t="n">
+        <v>25</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>id_amostra</t>
+        </is>
+      </c>
+      <c r="E241" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>324</v>
+      </c>
+      <c r="B242" t="n">
+        <v>25</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>resultados_extraidos</t>
+        </is>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>325</v>
+      </c>
+      <c r="B243" t="n">
+        <v>25</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>registros_sample</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>326</v>
+      </c>
+      <c r="B244" t="n">
+        <v>25</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>registros_client</t>
+        </is>
+      </c>
+      <c r="E244" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>327</v>
+      </c>
+      <c r="B245" t="n">
+        <v>25</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>embalagens_extraidas</t>
+        </is>
+      </c>
+      <c r="E245" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>328</v>
+      </c>
+      <c r="B246" t="n">
+        <v>25</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>tabelas_auditadas</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>329</v>
+      </c>
+      <c r="B247" t="n">
+        <v>25</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>secoes_auditadas</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>330</v>
+      </c>
+      <c r="B248" t="n">
+        <v>25</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>alertas_tabela</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>331</v>
+      </c>
+      <c r="B249" t="n">
+        <v>25</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>alertas_secao</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>332</v>
+      </c>
+      <c r="B250" t="n">
+        <v>25</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>alertas_campo</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>333</v>
+      </c>
+      <c r="B251" t="n">
+        <v>25</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>erros_validacao</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>334</v>
+      </c>
+      <c r="B252" t="n">
+        <v>25</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>parametros_sem_nome</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>335</v>
+      </c>
+      <c r="B253" t="n">
+        <v>25</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>parametros_com_unidades_divergentes</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>inteiro</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>336</v>
+      </c>
+      <c r="B254" t="n">
+        <v>25</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>coerencia_temporal</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>337</v>
+      </c>
+      <c r="B255" t="n">
+        <v>25</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>nao</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>338</v>
+      </c>
+      <c r="B256" t="n">
+        <v>25</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>document_reconciliation_audit</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>observacao</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>texto</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F99"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
